--- a/results/HFF_GSE5406_13_5_5.xlsx
+++ b/results/HFF_GSE5406_13_5_5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="78">
   <si>
     <t>classifier</t>
   </si>
@@ -82,6 +82,9 @@
     <t>RND_FST</t>
   </si>
   <si>
+    <t>DEC_TRE</t>
+  </si>
+  <si>
     <t>BAGGNG</t>
   </si>
   <si>
@@ -91,36 +94,33 @@
     <t>3NN_OVO</t>
   </si>
   <si>
+    <t>7NN_MUL</t>
+  </si>
+  <si>
+    <t>7NN_OVR</t>
+  </si>
+  <si>
     <t>1NN_OVO</t>
   </si>
   <si>
+    <t>5NN_OVR</t>
+  </si>
+  <si>
+    <t>5NN_MUL</t>
+  </si>
+  <si>
+    <t>3NN_MUL</t>
+  </si>
+  <si>
+    <t>3NN_OVR</t>
+  </si>
+  <si>
     <t>MLP</t>
   </si>
   <si>
-    <t>3NN_OVR</t>
-  </si>
-  <si>
-    <t>3NN_MUL</t>
-  </si>
-  <si>
-    <t>DEC_TRE</t>
-  </si>
-  <si>
     <t>5NN_OVO</t>
   </si>
   <si>
-    <t>5NN_OVR</t>
-  </si>
-  <si>
-    <t>5NN_MUL</t>
-  </si>
-  <si>
-    <t>7NN_MUL</t>
-  </si>
-  <si>
-    <t>7NN_OVR</t>
-  </si>
-  <si>
     <t>7NN_OVO</t>
   </si>
   <si>
@@ -130,57 +130,63 @@
     <t>1NN_OVR</t>
   </si>
   <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
     <t>A8</t>
   </si>
   <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
     <t>xuyager</t>
   </si>
   <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.2192663564553217, 1.2719474674051017, 0.772616725309434, 1.2617709910728672, 1.2849305251656853, 0.835990364358486, 0.8946549244984991, 1.5760047211283907, 2.006356551860892, 2.001572857313383, 1.949966610530351, 1.2308118646332027, 1.1919467070528436, 1.5975201957061167, 1.5881213427987775, 0.8833765848681205, 0.932364297394039, 2.7775601063115287, 1.902712285886648, 0.8529256395142941], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8371010617390235, 0.8166838583222915, 0.8139055606162098, 0.8581662866947254, 0.8549204366895786, 0.809924173334098, 0.8391357005036473, 0.8299098796264012, 0.8521299212395591, 0.8509594060856234, 0.8499026142148999, 0.8400438602998014, 0.8065889673534783, 0.7912596638794729, 0.8458365714507948, 0.8197344138732376, 0.8471184605060164, 0.8625974437010501, 0.8457719822568178, 0.8011704318486533], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8170686162753122, 0.786059532751481, 0.8112365926750859, 0.8374076708795708, 0.8360304275124739, 0.827767284344292, 0.8342659132678282, 0.8292719407274702, 0.8447352365376098, 0.8392679649769677, 0.858726504018338, 0.8362634724394448, 0.8037418522794478, 0.7857887708743702, 0.8502388390638435, 0.8056381945211073, 0.8386290707744145, 0.8742300187686065, 0.8285628516201772, 0.7964574714079685], \'MLPClassifier(max_iter=2000, random_state=13)\': [3.6718711297263136, 7.963761928522049, 0.9749548251157498, 1.5146927762987656, 1.3581072419405964, 1.5978157708505092, 1.5096201633439859, 2.9975416052089434, 1.5631546091103208, 2.4265703552738853, 5.881310534097332, 7.513608264332822, 2.7257124882433046, 5.451919279069887, 1.1766522472284204, 10.636010331478518, 0.950698060445922, 1.7888388540438673, 15.839730883586776, 1.0239440314991406], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.8542579042604553, 0.7052719329678341, 0.8261470806031591, 1.3067111612543556, 1.1401935158768575, 1.8585488221048299, 1.2707226783907655, 2.56757330221404, 1.0894782821155673, 1.0076481988484325, 1.5514040582229376, 0.9563393435540217, 1.0111893001096126, 0.7163193722476342, 1.0447386659889368, 0.8938819978907205, 1.1048813156793154, 1.0799799105873786, 1.02142435651168, 0.6689111271344375], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.230453334592005, 0.6891427845629022, 0.8085190508947351, 1.164185385770984, 1.3953775498020948, 5.030628214376591, 1.7821414474734736, 1.237540769658684, 1.0168880185156646, 0.9991221098937891, 3.1160360490005803, 1.2317479885064067, 0.9057902361351609, 1.8010277269016302, 1.255186141673926, 1.1700091228341374, 0.9426912310164398, 3.7032666602951987, 1.2131375054009534, 0.7370506492191128], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.7550402901152655, 0.7231363252403593, 0.7645122905930817, 0.7432617971365295, 0.8694358204040574, 0.7593892671845268, 0.8394024210757158, 0.8321747138116907, 0.8690703918953175, 0.7833505270939233, 0.8676847647384974, 0.7068265895658645, 0.7230457498970378, 0.6346137141901469, 0.8201037549560296, 0.847680082549093, 0.7865628039012621, 0.8831824828903541, 0.8243339559888674, 0.7622693178431711], \'SVC(C=1, random_state=13)\': [0.9053042166043666, 0.8626519830003119, 0.958503002955832, 0.9454884982825518, 1.0069655814309149, 0.9153219150721693, 0.9642714732942391, 0.976977019462647, 0.999060050453287, 1.0140879945393027, 0.9775162649906122, 0.9527455414267855, 0.9362429082686022, 0.9146226198690444, 0.9703794780139225, 0.9604376065113893, 0.9970381734656779, 1.038373473030262, 1.0151064790647515, 0.9641454166521793], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.7665471274731788, 0.778332219240853, 0.7663874680146752, 0.7761271122375311, 0.8585590568909551, 0.7706191867781985, 0.8939428967696998, 0.8333264691832013, 0.8480743587380476, 0.7995915936048489, 0.8786103963137573, 0.7288715682378203, 0.7776617822920022, 0.687603760623606, 0.8311161154234088, 0.8704137776377688, 0.8203310782166603, 0.8865034315374405, 0.8359015296387033, 0.773362464951079], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [15.555681988987406, 16.488054209915294, 18.21153013344867, 14.954281725272011, 18.97034388900903, 16.488054209915298, 18.590937011228853, 19.555599179201863, 17.452716377888308, 18.405269815719404, 16.31449574454777, 13.420509240628729, 18.21153013344867, 16.871497331076117, 16.31449574454777, 18.788712936880223, 15.555681988987406, 17.254940452236937, 16.693902622327947, 18.405269815719404], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.589950802600419, 4.372338311028312, 6.6045433748227325, 5.846975386332682, 6.206275871050679, 6.976990467848286, 4.323834054372089, 7.75250362736372, 3.9944040003986627, 8.835769249787067, 6.175850905178088, 3.9297597805285767, 5.082647809932451, 3.956339117583538, 6.544242032563226, 5.160093260860841, 6.2093041033922765, 7.366000058623624, 5.465082920054232, 5.517655630440289], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.951297277771864, 2.2355676714238104, 3.3575522995973635, 3.3044579339760527, 2.5697215780610376, 4.463546369120376, 2.5468425459482074, 4.882990468087145, 2.542455607898451, 3.7826529843390144, 3.011848267679976, 2.1497069683515995, 3.3072765339535395, 2.1451292008185643, 3.4120349457340717, 3.3108929566654677, 2.9535153938909753, 3.3924023880075427, 2.659588475782185, 2.611757035415044], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.1343002526260269, 0.8721146332306919, 2.0629897027863526, 1.5230656792315782, 1.247241448173408, 2.3481408736447986, 2.2935245227104093, 0.8656991897633441, 1.9032302516135393, 1.286178667346649, 1.6239170566876902, 1.1063051436619413, 0.8743656494189431, 1.230764477927358, 0.889436793506519, 1.5343332048175633, 1.6596821468178202, 1.1175108451917124, 0.8253829569142896, 1.6115320415284857], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8012416558784344, 0.8090163788326638, 0.890693965523292, 0.821853083867895, 0.871997930048919, 0.8253950529516079, 0.8361372193735203, 0.8139512000398037, 0.8247623344352824, 0.8497071958529365, 0.8322081250515875, 0.7845262201361933, 0.8296898923914746, 0.8199744975560391, 0.8121550050046787, 0.8146422332138323, 0.8790729148525869, 1.1585785845391707, 0.8472252018636958, 0.8344189490849893], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8140614964899823, 0.812588089340507, 0.8899384412857663, 0.8225734760107988, 0.8584553994460337, 0.8304148455620706, 0.8174374776396678, 0.8129607486660637, 0.8067968331011319, 0.8333006841304154, 0.7946870282697687, 0.7974328682972854, 0.811614600021613, 0.8023940452067903, 0.8151061554461532, 0.806258389037511, 0.8259388273238667, 0.8153646908916808, 0.8311343804428412, 0.85299271621312], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.6378438203903096, 2.758802999284735, 1.0597557612910586, 1.1056798332599476, 1.3517273396592415, 1.8607518681796587, 0.7876553673547252, 4.716375249374006, 0.7132601621428963, 0.8816492337614475, 7.036250771097349, 2.9933782114657626, 2.24794412060142, 1.5954673358060807, 0.924717100022412, 1.0497904744672295, 5.0704923258288135, 1.6320084610227803, 2.3331489899896862, 2.5499177616470865], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.7869555270853629, 1.0951979839791617, 1.0764754722627305, 1.5709895793728328, 1.0546169258111937, 0.9299841639077624, 0.8122327290345922, 0.9144524804401667, 0.7575559804833972, 0.8958971045467672, 0.9050185486617703, 0.9265850810699973, 0.7430712264091094, 0.8299241838160926, 0.9851206052039698, 0.8351989905132823, 1.5022503401224532, 0.7362814870834689, 1.151518087023895, 0.8268705273722241], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [3.9721734150072843, 2.047164424408103, 4.369787836050839, 0.9901679343602275, 2.4989431564619267, 0.9823533711839293, 0.8327291393849404, 1.7297110750456197, 1.582106457178106, 1.251382349386006, 3.257172553437534, 1.9840031874607766, 2.6870935047939923, 1.19290923889082, 1.5528237699810454, 0.9062936509455066, 1.1863542403642728, 2.1275249562449137, 1.31691838090164, 1.2343741119142193], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8024911980146069, 0.7657931503128009, 0.8514125836200593, 0.72552090525706, 0.8193503184230608, 0.7706146918779908, 0.8168744338435433, 0.7742228796313957, 0.7305234283264039, 0.8036473394338361, 0.7969523771190122, 0.7891413345066508, 0.7625147525118539, 0.7493162518687481, 0.8006143379153491, 0.726157078695301, 0.8163391586482656, 0.7902320767133442, 0.7662572847945927, 0.7853532075252905], \'SVC(C=1, random_state=13)\': [1.001468649895714, 0.9322443416529075, 1.022164640078579, 1.0506150668827536, 1.0047902997494194, 0.9750931609513898, 1.020643722892681, 0.9539118082619902, 0.9825819376423066, 0.937209497517031, 0.9586717146301453, 0.9428199138072235, 0.9152394574917346, 0.9630715219041492, 0.9594117013633994, 0.9628616745906082, 0.9926077974328074, 0.9384829649769852, 0.9815146409939024, 0.957633318711367], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8285129177447932, 0.8095376629437817, 0.8850653049740581, 0.757706511872766, 0.8332799673177596, 0.7797429805053974, 0.797864240468173, 0.7753359114614218, 0.7632455095199838, 0.7857528868209775, 0.7977299028079502, 0.8158745255384579, 0.7749634958055011, 0.7617090651823396, 0.8135236819126586, 0.7445106951110139, 0.8283683824687684, 0.8237333461655466, 0.7903677943284817, 0.8185835340471505], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [15.555681988987406, 16.488054209915294, 17.832123255668485, 14.187395482950366, 22.385005789030647, 15.721167967593653, 15.176275111207223, 18.78871293688022, 14.417461355646862, 16.871497331076114, 16.314495744547767, 17.254940452236937, 15.176275111207223, 17.638383573397753, 17.452716377888308, 14.57083860411119, 19.34975076678921, 17.638383573397757, 16.693902622327947, 15.33772484643283], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.155750457758251, 7.40843605911899, 8.785441690116482, 5.152719354684671, 9.575229001035108, 3.242877655056737, 6.110732919663346, 5.45685694446928, 4.683831716674722, 5.918352585988694, 4.653955340287805, 5.1367185313147115, 5.435897775609599, 6.967809125110465, 5.473619027593351, 4.720719337869937, 8.44251624289209, 5.928786939744135, 6.591739213514055, 8.119945925154582], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.751891889774221, 2.6823155005908834, 4.871660699894337, 2.301932827009337, 4.885324271613968, 1.0933486127243472, 3.6901039341805353, 3.3384609958019102, 3.246987070782239, 2.6876176612692606, 1.854636244979154, 2.9563910346652937, 2.9379445269775113, 2.247122881728805, 2.9840711231319723, 2.2119286329415404, 4.4659780257309265, 3.0017673337333504, 4.069678990429381, 3.4341398030293186], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9039915011762398, 1.9517673823427557, 2.036062771017774, 1.6062628302055832, 1.2193315614956288, 1.5526585092368286, 1.2438352111048536, 2.0262005978771342, 1.1870851546605663, 0.8168394618692603, 1.213104512053716, 1.6258290651502953, 1.5837276134075446, 1.278535588456574, 1.607377092714604, 0.8589713404832213, 2.0757469761966165, 1.1684440403016807, 0.8521377526914621, 1.179748946944047], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.7913414814940137, 0.821358580708411, 0.8260107318495828, 1.2197661174981071, 0.8327928920704041, 0.7986683308486348, 0.8151012829119024, 0.8571018958091756, 0.7946586601716265, 0.8152202681112483, 0.8248833229627676, 0.8145639393590464, 1.1924411157349364, 0.7914368515558933, 0.8874322895983889, 0.8429713361417743, 0.8212734070558578, 1.155656014707719, 0.8111058281316341, 0.8268734394227621], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.7964410262180902, 0.8018240681614452, 0.8289128728426346, 0.8591987662124739, 0.8461842540818667, 0.813076840411487, 0.8167390638222198, 0.8252999673478966, 0.8009062220270196, 0.804085023590842, 0.8089183352616945, 0.8045019052852935, 0.8344887079834075, 0.7989441545210649, 0.8914964583435163, 0.8223736373994348, 0.8162236349740376, 0.8157897204499933, 0.7868855352160434, 0.8116041563082186], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.3014234138763956, 7.055145260067771, 9.611422450831551, 2.6598059471536146, 1.3592134655191028, 7.6164712149081835, 2.0041495809673022, 4.869488520309016, 5.431464495933928, 3.527169775163321, 1.8182667382082451, 7.0342994213216175, 5.419108412950995, 1.9452081301849709, 1.4047708734833364, 5.288497010295467, 1.4561543833366573, 5.391528681975697, 4.363833467205561, 10.3258543783816], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.8461504653118455, 0.9034150228205516, 0.936508985137144, 0.9225266990207585, 1.042034331951375, 1.3097597811596655, 0.7706808060837603, 0.9450678488919555, 0.8455172648714432, 0.7990650203840196, 1.7935964075314952, 0.7800298319096659, 0.8852833920033132, 0.795582395555737, 1.3745631352189012, 1.2006672830983536, 1.196065018923727, 1.406670474416478, 1.0043821944241187, 0.8817702164093947], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.121567614206799, 0.8778070329423904, 1.1488925730297082, 0.9647660649965797, 4.51526658506061, 1.1617364157002648, 1.2835766980768148, 0.9206524333471711, 0.8685519991556097, 1.0210506016323546, 1.2345717394863769, 2.514158054840067, 0.8830456796848085, 2.8886250720556617, 1.3567415329609478, 1.235295146377569, 1.1594045395826598, 1.0433816913384526, 2.0829363258039266, 1.6585758819769438], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.7933113612572965, 0.7830552929771607, 0.7814360869692847, 0.6863142463212735, 0.8155331886531196, 0.7940110482564228, 0.7650520342164754, 0.749158861748177, 0.7771342333377562, 0.6993150420179334, 0.7295858972963302, 0.6918887486996635, 0.8037990105330463, 0.6961742067326833, 0.9399453005629079, 0.9071576232535554, 0.8075306351872136, 0.7684280544673598, 0.8098780760824416, 0.8084278900471401], \'SVC(C=1, random_state=13)\': [0.9408907420455421, 0.938093080720138, 0.9159581743418953, 0.9207350794575035, 0.9775662920735484, 0.9310811301431275, 0.9699895524693676, 0.9787220724484221, 0.94034760082205, 0.9259796128707043, 0.9918999616807371, 0.9366493934922715, 1.0149390163772558, 0.9408984317195792, 1.0200075142321563, 0.9992516801762861, 0.9593115264671094, 0.9513741223798141, 1.0027596312910687, 0.9635358805376961], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8096979025479424, 0.7950069220986372, 0.7930875806733091, 0.7193299734539126, 0.8270558422161034, 0.8174262601848566, 0.787502821805225, 0.7726938873902335, 0.788693232233855, 0.7545987591929337, 0.7626337651897884, 0.7056865736832287, 0.8270709608811211, 0.7195907065374009, 0.9528421558905191, 0.9306167088347433, 0.8292375048538183, 0.7806423888769738, 0.8107351213241405, 0.7894432025718429], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [16.31449574454777, 19.555599179201863, 15.555681988987407, 16.104611088754478, 14.038054477866684, 16.104611088754478, 17.832123255668492, 16.871497331076114, 16.31449574454777, 14.954281725272013, 15.555681988987406, 17.638383573397757, 17.073309500108127, 13.037066119467909, 17.832123255668492, 17.254940452236937, 15.555681988987411, 15.721167967593654, 15.176275111207223, 16.488054209915298], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.920620678001807, 7.3807478709759655, 6.601515142481135, 4.419642195664603, 5.373808022436455, 3.244130666074358, 6.187963834544478, 6.989930843638975, 7.723903382171401, 5.826106678821794, 4.708748807349791, 6.615114639671944, 5.816544474817743, 5.132405072717815, 9.169665211151896, 8.08919728943228, 4.3572872525862785, 5.864229220720262, 5.463843098626267, 6.152365987134911], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.992737994039498, 4.487185407602644, 4.054096244427708, 1.5630368949001008, 3.7162982613838254, 2.6034442457521205, 4.059354471976625, 3.3787754322047556, 2.661806591901297, 3.6835996020014647, 2.1887759370158255, 4.083862281012418, 2.5820960341642407, 2.5461282784363464, 5.26597097082211, 3.7896046194392214, 2.6279236884816317, 3.6841540275454965, 3.3046780068174186, 4.0541023473716], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.312071921486952, 0.8816020976619416, 1.2306482324891128, 0.8589569031328514, 1.2480237744558456, 0.8315165867635717, 2.612121565302346, 0.8951542913519678, 1.9915500434954891, 1.17836578127038, 0.9311812641913294, 1.5305443644689, 1.749436951600246, 1.238299056226165, 1.2405549248246002, 1.1813864159043903, 1.5874356261319038, 1.569569698438975, 1.552777187771277, 0.8238120408634547], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.2142722023441523, 0.8049773710840339, 0.8352654718052624, 0.8367089863915808, 0.8944179309636222, 0.8243408404601068, 0.8224349044896171, 0.8407216745316997, 0.8687795948873012, 1.138535675405468, 0.8538970727855014, 0.7999679910269714, 0.8891865368008143, 0.8293310674375918, 0.8793064347394115, 0.8137276515015556, 0.860265803081768, 0.8270898130765383, 0.8050948414108514, 0.7681176107923613], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8602991566887538, 0.8237373534977265, 0.8514077784947472, 0.8256186838197982, 0.862149756687037, 0.7959235366479748, 0.832315362005052, 0.8250707337730102, 0.8884284022956436, 0.8067473078746366, 0.8306247175157923, 0.812621941467262, 0.8574208583171881, 0.8277512934897009, 0.8472349623287865, 0.7971768559699582, 0.8330523404970176, 0.80241595271709, 0.7998877605915637, 0.785690630073013], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.8165309455236254, 2.518502009045868, 7.818830543864878, 1.5237591790074445, 1.0243219684587799, 1.0715547298445531, 2.354461523252146, 4.874300784464819, 2.1516035269772678, 1.8597537388764434, 6.522064655173008, 2.1679082501825806, 2.46596276248894, 10.248655061782667, 3.0604797150056324, 1.16694912950177, 8.319565614784848, 7.27749635459109, 6.654313448662844, 3.8275455937698233], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.3017455048546567, 1.0752058388732442, 1.0604808064260762, 0.8265339788495287, 1.270968409548325, 1.0860499109107564, 1.0309556443238193, 1.2877082023243929, 1.1372903057677948, 0.7928509172706002, 1.109706120915973, 0.898992899641378, 1.2760401349042252, 0.9863518945875503, 1.0047285269856499, 1.0587241298427814, 1.672242640453029, 0.9079859976697033, 0.8463037354377421, 0.7954575826981772], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.2501595014964297, 2.1804286677805074, 2.117511703027235, 0.8530035132008305, 1.1983723153212753, 3.878704904909456, 0.8541062274706972, 1.152965984103789, 1.1843678455024067, 1.914572025014539, 1.1213817666311394, 1.683935799784495, 1.7009178317046956, 1.077436963286669, 1.0813131951901782, 1.2756022925212855, 3.2685649231030522, 0.9038437204028925, 0.8778825334715715, 3.5309157543406697], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8821859495257321, 0.8211482943651256, 0.8255124255899743, 0.736514785188247, 0.8407479356972648, 0.7535817292741204, 0.7998326044397732, 0.8171398834163782, 0.8998202693594849, 0.727051350183984, 0.7746146621176072, 0.7578835192376768, 0.8474704760204552, 0.8544458970230735, 0.7845453878857961, 0.7644340643612805, 0.7128292102477103, 0.7341362701311133, 0.7534361972962935, 0.7115558758860185], \'SVC(C=1, random_state=13)\': [0.9855193591330221, 0.9958408407911238, 0.9723436725172363, 0.9803625643650776, 0.9753338132929413, 0.9315136757845718, 0.9291372341906103, 0.9474079407961418, 0.9504681582641793, 0.9219140848246326, 0.9759575248695285, 0.976603301475043, 1.0551923653406499, 1.018333989177164, 0.9296478639080309, 0.9526141130558569, 0.9498013551909567, 0.9550413270577576, 0.9795647618014637, 0.935795786567588], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9158325067224925, 0.8533937355636028, 0.8260635602716464, 0.7481915226178405, 0.8618807881775892, 0.7542118000403625, 0.8229789921712288, 0.8510868865042804, 0.8734459439978048, 0.7469585495213183, 0.7900242379348821, 0.7589586774932245, 0.8818685451927778, 0.8765390613401142, 0.8173272047934932, 0.7555818710563863, 0.7141339902658687, 0.7612941380132265, 0.7649070773670809, 0.736054505765432], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [17.452716377888304, 16.488054209915294, 18.21153013344867, 18.788712936880216, 17.073309500108124, 16.104611088754478, 16.31449574454777, 16.488054209915294, 18.59093701122885, 15.721167967593653, 17.452716377888308, 17.254940452236937, 16.693902622327947, 15.721167967593654, 15.555681988987406, 18.02182669455858, 18.97034388900903, 18.021826694558577, 14.796868233427043, 17.638383573397753], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.965638216096714, 4.387640548924683, 6.5381855678800305, 6.282180010656247, 5.837742101208928, 6.543183014471902, 5.476647259934945, 7.720501980623799, 7.679983023047843, 6.218176717176407, 6.21605180001776, 4.372892736572344, 6.564891069468734, 8.0825219687297, 4.695396056555438, 4.766215785944576, 5.459026455371036, 6.306109165746408, 4.694704824613151, 6.640995391253318], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.451815158714089, 1.5432890439387639, 3.676907482766639, 2.652435417943483, 2.61196053146295, 2.9504022939748142, 2.6788669278913275, 3.7550969506640586, 4.817869285699916, 2.591058295505466, 3.0015730434156875, 2.604010676757639, 3.39732348923156, 3.6910113213108744, 3.2967023678521814, 1.863547606099915, 2.967559376627616, 1.9341060712757547, 2.2506041634521576, 2.986320935907422], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.2624319040698637, 1.2530701693306878, 1.2577484304730888, 1.7227090649885726, 1.3612201329272442, 2.0345226830187304, 1.3036185876374715, 1.223779461394817, 1.2263289057697153, 0.8998422022421216, 1.9952663987940127, 1.1582266087765318, 1.5632793574908523, 1.2097965653038747, 0.772467291511344, 1.2100633061288972, 1.1872509268391784, 0.8661632735965938, 2.666982643694693, 0.8456794561052877], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8465161730832321, 0.8717310386330078, 0.8601955600253451, 0.8676340417516019, 0.8923405519434694, 0.9252078071685683, 0.8765408800363454, 0.8001875048036119, 1.1345620351939962, 0.8298431807279978, 0.890888429055218, 0.8346371213323331, 0.8216786500498707, 0.8103753137516481, 0.8239704893545293, 0.7917078966089681, 0.8196029102463878, 0.8039739000824027, 0.8412694691743271, 0.8114318204963546], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8282062494472837, 0.8660004383501851, 0.8833578711767284, 0.8435198245257488, 0.8902646054846991, 0.8978335675151528, 0.8443154964975244, 0.7868533431232899, 1.143022475061773, 0.8073836337101058, 0.8401919839881724, 0.8155382139157155, 0.8252535004732462, 0.8137032867150825, 0.8148117686576108, 0.8028585160014847, 0.808489692862336, 0.8081584520418371, 0.8246670975700877, 0.8136606281146039], \'MLPClassifier(max_iter=2000, random_state=13)\': [8.7061475508721, 8.115963626818262, 2.9890860487938324, 2.0411276656961115, 2.003595782039897, 4.825424234984969, 3.5368605659672343, 8.201111548746157, 1.7153401609226242, 3.4923337659289033, 3.1935485916025153, 2.5369340914096488, 5.386773303134749, 3.6997949513881485, 0.7791671334521347, 2.032070300480039, 9.00820348189857, 3.1349147434582627, 4.667621635170633, 10.948606901562526], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.2489751685323396, 1.0866570732024396, 1.392100044213247, 1.1799045090766926, 1.0839987316169586, 1.5715689240610986, 0.8483253526306147, 0.8205714074057225, 0.9584966410828288, 1.0513867903580933, 1.0214537589930859, 0.9530085777454465, 1.1854453919849914, 2.143110687015543, 0.7410933401093612, 0.9407328898990996, 1.4828301140963982, 2.003445625472146, 0.9423960976557728, 0.7890998270314983], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.639963695675144, 1.1708160936103087, 1.6684274428757682, 1.4482553802838714, 1.2009337810109186, 1.5237767699249327, 2.269976995347051, 0.8723478493422011, 0.87053755799885, 1.1051863593571978, 1.7259478619148063, 0.9873283474912401, 1.4235683339195593, 2.7504876263471925, 0.7714751863455263, 0.9203396416540529, 1.249914116942023, 0.8538207530039414, 1.1912062536441317, 0.7961262929278418], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.7194200432701326, 0.794713311091958, 0.9474138070576766, 0.870088523903005, 0.8573484840508009, 1.0116080938963423, 0.7437232264144812, 0.7125940196118367, 0.7224164370582851, 0.7040482512609539, 0.7432531432040745, 0.7926021844246031, 0.8811474117788415, 0.7322678286373022, 0.7170554983129427, 0.7246818057278308, 0.8253918638971287, 0.6895723710191992, 0.7221162003984515, 0.7271541574128177], \'SVC(C=1, random_state=13)\': [0.9736433966437176, 0.9000736653210407, 1.0697067743856332, 0.954440045136647, 1.0213290092614549, 1.1216133550061893, 0.9786317336072904, 0.9714158929809705, 0.9954062376707865, 0.9192456726946905, 0.9541490296898146, 1.0103911305092195, 0.9236845747033859, 0.9847321817441251, 0.9962476114883136, 0.9326069151943858, 0.9671093272678003, 0.9379366866441609, 0.9735657118922861, 0.9646290486617346], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.742733212845661, 0.8303240304051412, 0.9709303448588856, 0.8492747723329921, 0.8797107362726819, 1.0641851599317886, 0.7252133265650009, 0.6714436810854767, 0.7548635345258907, 0.7161427036871522, 0.793178955622941, 0.8043587622915594, 0.8838885899849859, 0.7341001634460093, 0.7395637216450118, 0.7370981804697649, 0.8152613473772146, 0.7330939761516624, 0.7543793616907335, 0.7921490860059517], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [17.452716377888308, 17.638383573397757, 20.10856452234957, 18.78871293688022, 18.21153013344867, 19.55559917920186, 16.314495744547767, 17.254940452236937, 17.073309500108124, 18.02182669455858, 20.108564522349575, 17.254940452236937, 16.314495744547767, 15.337724846432835, 16.693902622327947, 18.4052698157194, 17.832123255668492, 18.021826694558577, 15.176275111207223, 17.254940452236934], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.2117837462482, 6.62930802648025, 10.262868306397534, 3.66820235116889, 4.38110716429, 10.059283249487192, 5.4572380444574, 4.422148217699846, 5.446222294062356, 5.519463067001943, 8.083758402017418, 5.878977033072601, 5.804431545451352, 4.397520477136094, 4.315989178775259, 7.374626975817416, 5.428052900012769, 5.46423085064545, 3.93355406865348, 4.754528421171511], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [3.3362120307495653, 2.9638970953095334, 5.626897633627426, 2.6137464450394945, 1.8592525347742508, 5.714698738368802, 2.6695325832179306, 2.5630679852930616, 2.933246768002475, 2.257941693426971, 4.4796415974505575, 2.253810207892874, 3.001012574841805, 2.5461402838978335, 2.2156733752496116, 3.7299027790947883, 3.6688129595212042, 3.66315316556654, 2.217699554723642, 3.2550943093034546], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}'}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.2192663564553217, 1.2719474674051017, 0.772616725309434, 1.2617709910728672, 1.2849305251656853, 0.835990364358486, 0.8946549244984991, 1.5760047211283907, 2.006356551860892, 2.001572857313383, 1.949966610530351, 1.2308118646332027, 1.1919467070528436, 1.5975201957061167, 1.5881213427987775, 0.8833765848681205, 0.932364297394039, 2.7775601063115287, 1.902712285886648, 0.8529256395142941], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8371010617390235, 0.8166838583222915, 0.8139055606162098, 0.8581662866947254, 0.8549204366895786, 0.809924173334098, 0.8391357005036473, 0.8299098796264012, 0.8521299212395591, 0.8509594060856234, 0.8499026142148999, 0.8400438602998014, 0.8065889673534783, 0.7912596638794729, 0.8458365714507948, 0.8197344138732376, 0.8471184605060164, 0.8625974437010501, 0.8457719822568178, 0.8011704318486533], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8170686162753122, 0.786059532751481, 0.8112365926750859, 0.8374076708795708, 0.8360304275124739, 0.827767284344292, 0.8342659132678282, 0.8292719407274702, 0.8447352365376098, 0.8392679649769677, 0.858726504018338, 0.8362634724394448, 0.8037418522794478, 0.7857887708743702, 0.8502388390638435, 0.8056381945211073, 0.8386290707744145, 0.8742300187686065, 0.8285628516201772, 0.7964574714079685], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [3.6718711297263136, 7.963761928522049, 0.9749548251157498, 1.5146927762987656, 1.3581072419405964, 1.5978157708505092, 1.5096201633439859, 2.9975416052089434, 1.5631546091103208, 2.4265703552738853, 5.881310534097332, 7.513608264332822, 2.7257124882433046, 5.451919279069887, 1.1766522472284204, 10.636010331478518, 0.950698060445922, 1.7888388540438673, 15.839730883586776, 1.0239440314991406], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.8542579042604553, 0.7052719329678341, 0.8261470806031591, 1.3067111612543556, 1.1401935158768575, 1.8585488221048299, 1.2707226783907655, 2.56757330221404, 1.0894782821155673, 1.0076481988484325, 1.5514040582229376, 0.9563393435540217, 1.0111893001096126, 0.7163193722476342, 1.0447386659889368, 0.8938819978907205, 1.1048813156793154, 1.0799799105873786, 1.02142435651168, 0.6689111271344375], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.230453334592005, 0.6891427845629022, 0.8085190508947351, 1.164185385770984, 1.3953775498020948, 5.030628214376591, 1.7821414474734736, 1.237540769658684, 1.0168880185156646, 0.9991221098937891, 3.1160360490005803, 1.2317479885064067, 0.9057902361351609, 1.8010277269016302, 1.255186141673926, 1.1700091228341374, 0.9426912310164398, 3.7032666602951987, 1.2131375054009534, 0.7370506492191128], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.7550402901152655, 0.7231363252403593, 0.7645122905930817, 0.7432617971365295, 0.8694358204040574, 0.7593892671845268, 0.8394024210757158, 0.8321747138116907, 0.8690703918953175, 0.7833505270939233, 0.8676847647384974, 0.7068265895658645, 0.7230457498970378, 0.6346137141901469, 0.8201037549560296, 0.847680082549093, 0.7865628039012621, 0.8831824828903541, 0.8243339559888674, 0.7622693178431711], \'SVC(C=1, random_state=13)\': [0.9053042166043666, 0.8626519830003119, 0.958503002955832, 0.9454884982825518, 1.0069655814309149, 0.9153219150721693, 0.9642714732942391, 0.976977019462647, 0.999060050453287, 1.0140879945393027, 0.9775162649906122, 0.9527455414267855, 0.9362429082686022, 0.9146226198690444, 0.9703794780139225, 0.9604376065113893, 0.9970381734656779, 1.038373473030262, 1.0151064790647515, 0.9641454166521793], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.7665471274731788, 0.778332219240853, 0.7663874680146752, 0.7761271122375311, 0.8585590568909551, 0.7706191867781985, 0.8939428967696998, 0.8333264691832013, 0.8480743587380476, 0.7995915936048489, 0.8786103963137573, 0.7288715682378203, 0.7776617822920022, 0.687603760623606, 0.8311161154234088, 0.8704137776377688, 0.8203310782166603, 0.8865034315374405, 0.8359015296387033, 0.773362464951079], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [15.555681988987406, 16.488054209915294, 18.21153013344867, 14.954281725272011, 18.97034388900903, 16.488054209915298, 18.590937011228853, 19.555599179201863, 17.452716377888308, 18.405269815719404, 16.31449574454777, 13.420509240628729, 18.21153013344867, 16.871497331076117, 16.31449574454777, 18.788712936880223, 15.555681988987406, 17.254940452236937, 16.693902622327947, 18.405269815719404], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.589950802600419, 4.372338311028312, 6.6045433748227325, 5.846975386332682, 6.206275871050679, 6.976990467848286, 4.323834054372089, 7.75250362736372, 3.9944040003986627, 8.835769249787067, 6.175850905178088, 3.9297597805285767, 5.082647809932451, 3.956339117583538, 6.544242032563226, 5.160093260860841, 6.2093041033922765, 7.366000058623624, 5.465082920054232, 5.517655630440289], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.951297277771864, 2.2355676714238104, 3.3575522995973635, 3.3044579339760527, 2.5697215780610376, 4.463546369120376, 2.5468425459482074, 4.882990468087145, 2.542455607898451, 3.7826529843390144, 3.011848267679976, 2.1497069683515995, 3.3072765339535395, 2.1451292008185643, 3.4120349457340717, 3.3108929566654677, 2.9535153938909753, 3.3924023880075427, 2.659588475782185, 2.611757035415044]}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.1343002526260269, 0.8721146332306919, 2.0629897027863526, 1.5230656792315782, 1.247241448173408, 2.3481408736447986, 2.2935245227104093, 0.8656991897633441, 1.9032302516135393, 1.286178667346649, 1.6239170566876902, 1.1063051436619413, 0.8743656494189431, 1.230764477927358, 0.889436793506519, 1.5343332048175633, 1.6596821468178202, 1.1175108451917124, 0.8253829569142896, 1.6115320415284857], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8012416558784344, 0.8090163788326638, 0.890693965523292, 0.821853083867895, 0.871997930048919, 0.8253950529516079, 0.8361372193735203, 0.8139512000398037, 0.8247623344352824, 0.8497071958529365, 0.8322081250515875, 0.7845262201361933, 0.8296898923914746, 0.8199744975560391, 0.8121550050046787, 0.8146422332138323, 0.8790729148525869, 1.1585785845391707, 0.8472252018636958, 0.8344189490849893], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8140614964899823, 0.812588089340507, 0.8899384412857663, 0.8225734760107988, 0.8584553994460337, 0.8304148455620706, 0.8174374776396678, 0.8129607486660637, 0.8067968331011319, 0.8333006841304154, 0.7946870282697687, 0.7974328682972854, 0.811614600021613, 0.8023940452067903, 0.8151061554461532, 0.806258389037511, 0.8259388273238667, 0.8153646908916808, 0.8311343804428412, 0.85299271621312], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.6378438203903096, 2.758802999284735, 1.0597557612910586, 1.1056798332599476, 1.3517273396592415, 1.8607518681796587, 0.7876553673547252, 4.716375249374006, 0.7132601621428963, 0.8816492337614475, 7.036250771097349, 2.9933782114657626, 2.24794412060142, 1.5954673358060807, 0.924717100022412, 1.0497904744672295, 5.0704923258288135, 1.6320084610227803, 2.3331489899896862, 2.5499177616470865], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.7869555270853629, 1.0951979839791617, 1.0764754722627305, 1.5709895793728328, 1.0546169258111937, 0.9299841639077624, 0.8122327290345922, 0.9144524804401667, 0.7575559804833972, 0.8958971045467672, 0.9050185486617703, 0.9265850810699973, 0.7430712264091094, 0.8299241838160926, 0.9851206052039698, 0.8351989905132823, 1.5022503401224532, 0.7362814870834689, 1.151518087023895, 0.8268705273722241], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [3.9721734150072843, 2.047164424408103, 4.369787836050839, 0.9901679343602275, 2.4989431564619267, 0.9823533711839293, 0.8327291393849404, 1.7297110750456197, 1.582106457178106, 1.251382349386006, 3.257172553437534, 1.9840031874607766, 2.6870935047939923, 1.19290923889082, 1.5528237699810454, 0.9062936509455066, 1.1863542403642728, 2.1275249562449137, 1.31691838090164, 1.2343741119142193], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8024911980146069, 0.7657931503128009, 0.8514125836200593, 0.72552090525706, 0.8193503184230608, 0.7706146918779908, 0.8168744338435433, 0.7742228796313957, 0.7305234283264039, 0.8036473394338361, 0.7969523771190122, 0.7891413345066508, 0.7625147525118539, 0.7493162518687481, 0.8006143379153491, 0.726157078695301, 0.8163391586482656, 0.7902320767133442, 0.7662572847945927, 0.7853532075252905], \'SVC(C=1, random_state=13)\': [1.001468649895714, 0.9322443416529075, 1.022164640078579, 1.0506150668827536, 1.0047902997494194, 0.9750931609513898, 1.020643722892681, 0.9539118082619902, 0.9825819376423066, 0.937209497517031, 0.9586717146301453, 0.9428199138072235, 0.9152394574917346, 0.9630715219041492, 0.9594117013633994, 0.9628616745906082, 0.9926077974328074, 0.9384829649769852, 0.9815146409939024, 0.957633318711367], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8285129177447932, 0.8095376629437817, 0.8850653049740581, 0.757706511872766, 0.8332799673177596, 0.7797429805053974, 0.797864240468173, 0.7753359114614218, 0.7632455095199838, 0.7857528868209775, 0.7977299028079502, 0.8158745255384579, 0.7749634958055011, 0.7617090651823396, 0.8135236819126586, 0.7445106951110139, 0.8283683824687684, 0.8237333461655466, 0.7903677943284817, 0.8185835340471505], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [15.555681988987406, 16.488054209915294, 17.832123255668485, 14.187395482950366, 22.385005789030647, 15.721167967593653, 15.176275111207223, 18.78871293688022, 14.417461355646862, 16.871497331076114, 16.314495744547767, 17.254940452236937, 15.176275111207223, 17.638383573397753, 17.452716377888308, 14.57083860411119, 19.34975076678921, 17.638383573397757, 16.693902622327947, 15.33772484643283], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.155750457758251, 7.40843605911899, 8.785441690116482, 5.152719354684671, 9.575229001035108, 3.242877655056737, 6.110732919663346, 5.45685694446928, 4.683831716674722, 5.918352585988694, 4.653955340287805, 5.1367185313147115, 5.435897775609599, 6.967809125110465, 5.473619027593351, 4.720719337869937, 8.44251624289209, 5.928786939744135, 6.591739213514055, 8.119945925154582], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.751891889774221, 2.6823155005908834, 4.871660699894337, 2.301932827009337, 4.885324271613968, 1.0933486127243472, 3.6901039341805353, 3.3384609958019102, 3.246987070782239, 2.6876176612692606, 1.854636244979154, 2.9563910346652937, 2.9379445269775113, 2.247122881728805, 2.9840711231319723, 2.2119286329415404, 4.4659780257309265, 3.0017673337333504, 4.069678990429381, 3.4341398030293186]}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9039915011762398, 1.9517673823427557, 2.036062771017774, 1.6062628302055832, 1.2193315614956288, 1.5526585092368286, 1.2438352111048536, 2.0262005978771342, 1.1870851546605663, 0.8168394618692603, 1.213104512053716, 1.6258290651502953, 1.5837276134075446, 1.278535588456574, 1.607377092714604, 0.8589713404832213, 2.0757469761966165, 1.1684440403016807, 0.8521377526914621, 1.179748946944047], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.7913414814940137, 0.821358580708411, 0.8260107318495828, 1.2197661174981071, 0.8327928920704041, 0.7986683308486348, 0.8151012829119024, 0.8571018958091756, 0.7946586601716265, 0.8152202681112483, 0.8248833229627676, 0.8145639393590464, 1.1924411157349364, 0.7914368515558933, 0.8874322895983889, 0.8429713361417743, 0.8212734070558578, 1.155656014707719, 0.8111058281316341, 0.8268734394227621], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.7964410262180902, 0.8018240681614452, 0.8289128728426346, 0.8591987662124739, 0.8461842540818667, 0.813076840411487, 0.8167390638222198, 0.8252999673478966, 0.8009062220270196, 0.804085023590842, 0.8089183352616945, 0.8045019052852935, 0.8344887079834075, 0.7989441545210649, 0.8914964583435163, 0.8223736373994348, 0.8162236349740376, 0.8157897204499933, 0.7868855352160434, 0.8116041563082186], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.3014234138763956, 7.055145260067771, 9.611422450831551, 2.6598059471536146, 1.3592134655191028, 7.6164712149081835, 2.0041495809673022, 4.869488520309016, 5.431464495933928, 3.527169775163321, 1.8182667382082451, 7.0342994213216175, 5.419108412950995, 1.9452081301849709, 1.4047708734833364, 5.288497010295467, 1.4561543833366573, 5.391528681975697, 4.363833467205561, 10.3258543783816], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.8461504653118455, 0.9034150228205516, 0.936508985137144, 0.9225266990207585, 1.042034331951375, 1.3097597811596655, 0.7706808060837603, 0.9450678488919555, 0.8455172648714432, 0.7990650203840196, 1.7935964075314952, 0.7800298319096659, 0.8852833920033132, 0.795582395555737, 1.3745631352189012, 1.2006672830983536, 1.196065018923727, 1.406670474416478, 1.0043821944241187, 0.8817702164093947], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.121567614206799, 0.8778070329423904, 1.1488925730297082, 0.9647660649965797, 4.51526658506061, 1.1617364157002648, 1.2835766980768148, 0.9206524333471711, 0.8685519991556097, 1.0210506016323546, 1.2345717394863769, 2.514158054840067, 0.8830456796848085, 2.8886250720556617, 1.3567415329609478, 1.235295146377569, 1.1594045395826598, 1.0433816913384526, 2.0829363258039266, 1.6585758819769438], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.7933113612572965, 0.7830552929771607, 0.7814360869692847, 0.6863142463212735, 0.8155331886531196, 0.7940110482564228, 0.7650520342164754, 0.749158861748177, 0.7771342333377562, 0.6993150420179334, 0.7295858972963302, 0.6918887486996635, 0.8037990105330463, 0.6961742067326833, 0.9399453005629079, 0.9071576232535554, 0.8075306351872136, 0.7684280544673598, 0.8098780760824416, 0.8084278900471401], \'SVC(C=1, random_state=13)\': [0.9408907420455421, 0.938093080720138, 0.9159581743418953, 0.9207350794575035, 0.9775662920735484, 0.9310811301431275, 0.9699895524693676, 0.9787220724484221, 0.94034760082205, 0.9259796128707043, 0.9918999616807371, 0.9366493934922715, 1.0149390163772558, 0.9408984317195792, 1.0200075142321563, 0.9992516801762861, 0.9593115264671094, 0.9513741223798141, 1.0027596312910687, 0.9635358805376961], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8096979025479424, 0.7950069220986372, 0.7930875806733091, 0.7193299734539126, 0.8270558422161034, 0.8174262601848566, 0.787502821805225, 0.7726938873902335, 0.788693232233855, 0.7545987591929337, 0.7626337651897884, 0.7056865736832287, 0.8270709608811211, 0.7195907065374009, 0.9528421558905191, 0.9306167088347433, 0.8292375048538183, 0.7806423888769738, 0.8107351213241405, 0.7894432025718429], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [16.31449574454777, 19.555599179201863, 15.555681988987407, 16.104611088754478, 14.038054477866684, 16.104611088754478, 17.832123255668492, 16.871497331076114, 16.31449574454777, 14.954281725272013, 15.555681988987406, 17.638383573397757, 17.073309500108127, 13.037066119467909, 17.832123255668492, 17.254940452236937, 15.555681988987411, 15.721167967593654, 15.176275111207223, 16.488054209915298], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.920620678001807, 7.3807478709759655, 6.601515142481135, 4.419642195664603, 5.373808022436455, 3.244130666074358, 6.187963834544478, 6.989930843638975, 7.723903382171401, 5.826106678821794, 4.708748807349791, 6.615114639671944, 5.816544474817743, 5.132405072717815, 9.169665211151896, 8.08919728943228, 4.3572872525862785, 5.864229220720262, 5.463843098626267, 6.152365987134911], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.992737994039498, 4.487185407602644, 4.054096244427708, 1.5630368949001008, 3.7162982613838254, 2.6034442457521205, 4.059354471976625, 3.3787754322047556, 2.661806591901297, 3.6835996020014647, 2.1887759370158255, 4.083862281012418, 2.5820960341642407, 2.5461282784363464, 5.26597097082211, 3.7896046194392214, 2.6279236884816317, 3.6841540275454965, 3.3046780068174186, 4.0541023473716]}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.312071921486952, 0.8816020976619416, 1.2306482324891128, 0.8589569031328514, 1.2480237744558456, 0.8315165867635717, 2.612121565302346, 0.8951542913519678, 1.9915500434954891, 1.17836578127038, 0.9311812641913294, 1.5305443644689, 1.749436951600246, 1.238299056226165, 1.2405549248246002, 1.1813864159043903, 1.5874356261319038, 1.569569698438975, 1.552777187771277, 0.8238120408634547], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.2142722023441523, 0.8049773710840339, 0.8352654718052624, 0.8367089863915808, 0.8944179309636222, 0.8243408404601068, 0.8224349044896171, 0.8407216745316997, 0.8687795948873012, 1.138535675405468, 0.8538970727855014, 0.7999679910269714, 0.8891865368008143, 0.8293310674375918, 0.8793064347394115, 0.8137276515015556, 0.860265803081768, 0.8270898130765383, 0.8050948414108514, 0.7681176107923613], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8602991566887538, 0.8237373534977265, 0.8514077784947472, 0.8256186838197982, 0.862149756687037, 0.7959235366479748, 0.832315362005052, 0.8250707337730102, 0.8884284022956436, 0.8067473078746366, 0.8306247175157923, 0.812621941467262, 0.8574208583171881, 0.8277512934897009, 0.8472349623287865, 0.7971768559699582, 0.8330523404970176, 0.80241595271709, 0.7998877605915637, 0.785690630073013], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.8165309455236254, 2.518502009045868, 7.818830543864878, 1.5237591790074445, 1.0243219684587799, 1.0715547298445531, 2.354461523252146, 4.874300784464819, 2.1516035269772678, 1.8597537388764434, 6.522064655173008, 2.1679082501825806, 2.46596276248894, 10.248655061782667, 3.0604797150056324, 1.16694912950177, 8.319565614784848, 7.27749635459109, 6.654313448662844, 3.8275455937698233], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.3017455048546567, 1.0752058388732442, 1.0604808064260762, 0.8265339788495287, 1.270968409548325, 1.0860499109107564, 1.0309556443238193, 1.2877082023243929, 1.1372903057677948, 0.7928509172706002, 1.109706120915973, 0.898992899641378, 1.2760401349042252, 0.9863518945875503, 1.0047285269856499, 1.0587241298427814, 1.672242640453029, 0.9079859976697033, 0.8463037354377421, 0.7954575826981772], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.2501595014964297, 2.1804286677805074, 2.117511703027235, 0.8530035132008305, 1.1983723153212753, 3.878704904909456, 0.8541062274706972, 1.152965984103789, 1.1843678455024067, 1.914572025014539, 1.1213817666311394, 1.683935799784495, 1.7009178317046956, 1.077436963286669, 1.0813131951901782, 1.2756022925212855, 3.2685649231030522, 0.9038437204028925, 0.8778825334715715, 3.5309157543406697], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8821859495257321, 0.8211482943651256, 0.8255124255899743, 0.736514785188247, 0.8407479356972648, 0.7535817292741204, 0.7998326044397732, 0.8171398834163782, 0.8998202693594849, 0.727051350183984, 0.7746146621176072, 0.7578835192376768, 0.8474704760204552, 0.8544458970230735, 0.7845453878857961, 0.7644340643612805, 0.7128292102477103, 0.7341362701311133, 0.7534361972962935, 0.7115558758860185], \'SVC(C=1, random_state=13)\': [0.9855193591330221, 0.9958408407911238, 0.9723436725172363, 0.9803625643650776, 0.9753338132929413, 0.9315136757845718, 0.9291372341906103, 0.9474079407961418, 0.9504681582641793, 0.9219140848246326, 0.9759575248695285, 0.976603301475043, 1.0551923653406499, 1.018333989177164, 0.9296478639080309, 0.9526141130558569, 0.9498013551909567, 0.9550413270577576, 0.9795647618014637, 0.935795786567588], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9158325067224925, 0.8533937355636028, 0.8260635602716464, 0.7481915226178405, 0.8618807881775892, 0.7542118000403625, 0.8229789921712288, 0.8510868865042804, 0.8734459439978048, 0.7469585495213183, 0.7900242379348821, 0.7589586774932245, 0.8818685451927778, 0.8765390613401142, 0.8173272047934932, 0.7555818710563863, 0.7141339902658687, 0.7612941380132265, 0.7649070773670809, 0.736054505765432], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [17.452716377888304, 16.488054209915294, 18.21153013344867, 18.788712936880216, 17.073309500108124, 16.104611088754478, 16.31449574454777, 16.488054209915294, 18.59093701122885, 15.721167967593653, 17.452716377888308, 17.254940452236937, 16.693902622327947, 15.721167967593654, 15.555681988987406, 18.02182669455858, 18.97034388900903, 18.021826694558577, 14.796868233427043, 17.638383573397753], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.965638216096714, 4.387640548924683, 6.5381855678800305, 6.282180010656247, 5.837742101208928, 6.543183014471902, 5.476647259934945, 7.720501980623799, 7.679983023047843, 6.218176717176407, 6.21605180001776, 4.372892736572344, 6.564891069468734, 8.0825219687297, 4.695396056555438, 4.766215785944576, 5.459026455371036, 6.306109165746408, 4.694704824613151, 6.640995391253318], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.451815158714089, 1.5432890439387639, 3.676907482766639, 2.652435417943483, 2.61196053146295, 2.9504022939748142, 2.6788669278913275, 3.7550969506640586, 4.817869285699916, 2.591058295505466, 3.0015730434156875, 2.604010676757639, 3.39732348923156, 3.6910113213108744, 3.2967023678521814, 1.863547606099915, 2.967559376627616, 1.9341060712757547, 2.2506041634521576, 2.986320935907422]}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.2624319040698637, 1.2530701693306878, 1.2577484304730888, 1.7227090649885726, 1.3612201329272442, 2.0345226830187304, 1.3036185876374715, 1.223779461394817, 1.2263289057697153, 0.8998422022421216, 1.9952663987940127, 1.1582266087765318, 1.5632793574908523, 1.2097965653038747, 0.772467291511344, 1.2100633061288972, 1.1872509268391784, 0.8661632735965938, 2.666982643694693, 0.8456794561052877], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8465161730832321, 0.8717310386330078, 0.8601955600253451, 0.8676340417516019, 0.8923405519434694, 0.9252078071685683, 0.8765408800363454, 0.8001875048036119, 1.1345620351939962, 0.8298431807279978, 0.890888429055218, 0.8346371213323331, 0.8216786500498707, 0.8103753137516481, 0.8239704893545293, 0.7917078966089681, 0.8196029102463878, 0.8039739000824027, 0.8412694691743271, 0.8114318204963546], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8282062494472837, 0.8660004383501851, 0.8833578711767284, 0.8435198245257488, 0.8902646054846991, 0.8978335675151528, 0.8443154964975244, 0.7868533431232899, 1.143022475061773, 0.8073836337101058, 0.8401919839881724, 0.8155382139157155, 0.8252535004732462, 0.8137032867150825, 0.8148117686576108, 0.8028585160014847, 0.808489692862336, 0.8081584520418371, 0.8246670975700877, 0.8136606281146039], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [8.7061475508721, 8.115963626818262, 2.9890860487938324, 2.0411276656961115, 2.003595782039897, 4.825424234984969, 3.5368605659672343, 8.201111548746157, 1.7153401609226242, 3.4923337659289033, 3.1935485916025153, 2.5369340914096488, 5.386773303134749, 3.6997949513881485, 0.7791671334521347, 2.032070300480039, 9.00820348189857, 3.1349147434582627, 4.667621635170633, 10.948606901562526], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [1.2489751685323396, 1.0866570732024396, 1.392100044213247, 1.1799045090766926, 1.0839987316169586, 1.5715689240610986, 0.8483253526306147, 0.8205714074057225, 0.9584966410828288, 1.0513867903580933, 1.0214537589930859, 0.9530085777454465, 1.1854453919849914, 2.143110687015543, 0.7410933401093612, 0.9407328898990996, 1.4828301140963982, 2.003445625472146, 0.9423960976557728, 0.7890998270314983], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [1.639963695675144, 1.1708160936103087, 1.6684274428757682, 1.4482553802838714, 1.2009337810109186, 1.5237767699249327, 2.269976995347051, 0.8723478493422011, 0.87053755799885, 1.1051863593571978, 1.7259478619148063, 0.9873283474912401, 1.4235683339195593, 2.7504876263471925, 0.7714751863455263, 0.9203396416540529, 1.249914116942023, 0.8538207530039414, 1.1912062536441317, 0.7961262929278418], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.7194200432701326, 0.794713311091958, 0.9474138070576766, 0.870088523903005, 0.8573484840508009, 1.0116080938963423, 0.7437232264144812, 0.7125940196118367, 0.7224164370582851, 0.7040482512609539, 0.7432531432040745, 0.7926021844246031, 0.8811474117788415, 0.7322678286373022, 0.7170554983129427, 0.7246818057278308, 0.8253918638971287, 0.6895723710191992, 0.7221162003984515, 0.7271541574128177], \'SVC(C=1, random_state=13)\': [0.9736433966437176, 0.9000736653210407, 1.0697067743856332, 0.954440045136647, 1.0213290092614549, 1.1216133550061893, 0.9786317336072904, 0.9714158929809705, 0.9954062376707865, 0.9192456726946905, 0.9541490296898146, 1.0103911305092195, 0.9236845747033859, 0.9847321817441251, 0.9962476114883136, 0.9326069151943858, 0.9671093272678003, 0.9379366866441609, 0.9735657118922861, 0.9646290486617346], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.742733212845661, 0.8303240304051412, 0.9709303448588856, 0.8492747723329921, 0.8797107362726819, 1.0641851599317886, 0.7252133265650009, 0.6714436810854767, 0.7548635345258907, 0.7161427036871522, 0.793178955622941, 0.8043587622915594, 0.8838885899849859, 0.7341001634460093, 0.7395637216450118, 0.7370981804697649, 0.8152613473772146, 0.7330939761516624, 0.7543793616907335, 0.7921490860059517], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [17.452716377888308, 17.638383573397757, 20.10856452234957, 18.78871293688022, 18.21153013344867, 19.55559917920186, 16.314495744547767, 17.254940452236937, 17.073309500108124, 18.02182669455858, 20.108564522349575, 17.254940452236937, 16.314495744547767, 15.337724846432835, 16.693902622327947, 18.4052698157194, 17.832123255668492, 18.021826694558577, 15.176275111207223, 17.254940452236934], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.2117837462482, 6.62930802648025, 10.262868306397534, 3.66820235116889, 4.38110716429, 10.059283249487192, 5.4572380444574, 4.422148217699846, 5.446222294062356, 5.519463067001943, 8.083758402017418, 5.878977033072601, 5.804431545451352, 4.397520477136094, 4.315989178775259, 7.374626975817416, 5.428052900012769, 5.46423085064545, 3.93355406865348, 4.754528421171511], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [3.3362120307495653, 2.9638970953095334, 5.626897633627426, 2.6137464450394945, 1.8592525347742508, 5.714698738368802, 2.6695325832179306, 2.5630679852930616, 2.933246768002475, 2.257941693426971, 4.4796415974505575, 2.253810207892874, 3.001012574841805, 2.5461402838978335, 2.2156733752496116, 3.7299027790947883, 3.6688129595212042, 3.66315316556654, 2.217699554723642, 3.2550943093034546]}'}</t>
+  </si>
+  <si>
+    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
     <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
@@ -193,39 +199,12 @@
     <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02f7388c50&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02f4d077d0&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ed723d10&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4d06750&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f739a250&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4d23010&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02f4d20690&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02f4d23c50&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02f4d20f90&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4d23c90&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ef1a8a50&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4d23710&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a1634bed0&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f19f873f710&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f19f877ea50&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19f873c190&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19f877d750&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19f877c6d0&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f19f877c890&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f19f877c7d0&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f19f877f990&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f19f877c490&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f19f877e690&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f19f877d590&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c24a0f50&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f27ad0&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f492d0&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2f25950&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2f4be50&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2f48ad0&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2f4b5d0&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2f4a090&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2f4b410&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f4bad0&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f48910&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f48450&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69f33f10&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69f5bdd0&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5c488d10&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69f59b50&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5c48af10&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5c488150&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5c488ad0&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5c48b210&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5c4890d0&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c48ad10&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c48b8d0&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c488510&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d8f1f50&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d2be010&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d2c06d0&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d8df1d0&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d2c1f10&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d2c0190&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e199b2350&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d2c03d0&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d2c1050&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e19801e50&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d2c3f90&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d2c21d0&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5c46ba50&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69e81c50&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69d89d90&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69e80090&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69d88dd0&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69d891d0&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69d8bb90&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69d8bad0&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69d89890&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69d8a310&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69d8b4d0&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69d8a110&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d903190&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d8a2a10&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d928350&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e1980d8d0&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e1999ca90&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e1999cf10&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e1999e1d0&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e1999c550&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e1999fad0&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d8a1e50&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d928a50&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e1999f2d0&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a16a37090&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a2c6d10&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a16359050&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19f877f190&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a746f50&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a1636a590&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a1636a150&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a1636af10&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a1636b090&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a16369a90&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a1636be50&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a16368590&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ed6f3910&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb06750&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ed6f6690&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4d21cd0&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ed742a90&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ed743bd0&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed7416d0&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed740510&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed740810&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4eb9e50&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed740150&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed740b10&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8a78750&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8c07190&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c24d4050&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8a5e990&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c28be610&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8c1b8d0&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8c19cd0&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8c199d0&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8c19510&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8c18b50&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8c1b410&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8c1ba90&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c3316810&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8a88b10&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8c182d0&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8a88550&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8c44810&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2f33f10&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2ee81d0&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8a5e690&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8a5d950&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8c013d0&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8a5dd90&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c24a5d50&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69ed5910&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69ea74d0&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69d89e50&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69ea6410&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69f1a750&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69d9d250&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69d9c690&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69d9c6d0&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5d83c750&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69ea6250&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d814690&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d814890&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02f4e7e750&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02f4eb6f50&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb12210&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ed73b650&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4cf4fd0&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4cf7b10&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02f4d23210&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02f4d21b50&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02f7396110&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4d21e50&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed6f0a50&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f73969d0&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a14a3d890&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a1636bf90&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a256d90&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a16367190&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a256010&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a255bd0&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a256dd0&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a257c90&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a257090&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a2568d0&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a254390&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a255c90&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e199abed0&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e19813990&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e199a40d0&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e19812a10&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d9089d0&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e199a3310&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e19803250&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e199a3ad0&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e199a37d0&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d8d9e50&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e19810a50&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e197e8250&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d933190&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e199d0190&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d8f61d0&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0dd0d8d0&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e199aabd0&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e199a8710&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e199ab250&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d89f9d0&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d89d690&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0ce99e50&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d89ef10&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e197f1f10&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a2c3c90&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a255090&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a2b7690&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a161a7190&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a161929d0&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a285950&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0aeee210&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f19f874bed0&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f19f8749050&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f19f874bc90&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f19f8749d50&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f19f8748590&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2480210&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f31090&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f4c250&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c28cbb50&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2f3c810&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c24c6690&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2887ad0&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2885990&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2f15010&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c28d93d0&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f15d90&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f15110&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ed6dfc50&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ef189250&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb25910&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ecb13b10&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ef169550&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ef1e5c90&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ef1e6d10&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ef1e77d0&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed6e7550&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ef1a1e50&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ef188a50&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed6e78d0&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f6a053b50&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5c3d0c10&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5c4746d0&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5c476410&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69e77210&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69e6b950&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69e68a90&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5c4ae850&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5c4af010&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5e35e250&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c4afa50&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c4ae890&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69eed510&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69e790d0&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5c46b950&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69ee6410&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69f146d0&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69f15fd0&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69f36650&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69f37010&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69f36fd0&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69f37050&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69f37110&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69f36ed0&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb56750&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02f4e7bb10&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02f4ee40d0&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4e8b650&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4eb0190&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ed6dd610&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed7437d0&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed7434d0&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed743490&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed743550&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4ea8a50&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed743290&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2ef0790&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8c29210&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8c4e610&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c24d6a90&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8c1e210&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8c1e850&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8c1dd90&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8c26790&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2f4ee90&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f4e110&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8a66590&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8a67710&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a16363ed0&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f19f8710fd0&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f19f874af10&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a16377190&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19f8764710&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19f8767ed0&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7f19f8767e10&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7f19f8767b50&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a09be67d0&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a09be6650&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a09be6350&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a09be71d0&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d263190&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0ce9aa10&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d90be10&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d253b10&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d89bed0&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d2669d0&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d90b290&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d29ab50&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d29a8d0&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0cea1e50&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d928a50&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d29abd0&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d293190&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e1999e1d0&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e1999a210&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e199c5650&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d2a5210&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d2a4690&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e199ba350&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d2a5290&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d2a4650&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d8e1e50&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d270a50&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d2a4910&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a1635d0d0&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a29c550&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f19f8752950&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a23f190&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a1618bb90&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a16189a50&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a16188790&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a161bf550&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a161bfe90&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a161bfe10&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a161bff10&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a161bf050&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02f4d1ed10&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ef1c0b50&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb36750&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4e93650&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ef15b910&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ecb52210&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02f4eb7110&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ef1b6690&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ef1b5490&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ef149e50&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4e88650&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4ee6910&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f28f50&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8a6d990&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2edbb50&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c28a99d0&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c28b4910&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c28b6810&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8c4dfd0&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c28b6f10&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8a639d0&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c28b62d0&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f193d0&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8a632d0&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69e61190&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69e64690&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69f18a90&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69f3e410&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69e91a50&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69e90a10&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5c4ab690&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69ea0210&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69ea1910&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69ea1650&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69ea0450&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f69ea2010&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f38f50&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c28660d0&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2ebe610&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2ee8290&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2ef2d90&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2ef1b10&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2ef2f90&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2ef0ad0&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2ef1250&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c28662d0&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2ef14d0&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2ef11d0&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb48450&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb077d0&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb70ad0&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4d1b650&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ecb72290&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ecb73910&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ecb70910&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ecb72f90&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ecb73d10&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ecb72dd0&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ecb72650&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed6da090&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d925a50&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0ceade10&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0ceacc90&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0cead490&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0ceae7d0&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0ceaf910&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0ceae950&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0ceac810&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0cead990&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0ceacf50&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0ceae050&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e199ab210&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a237050&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a23ff10&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a0a23f310&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a161a7190&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a23fe90&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a23eb10&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a23c710&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a23c090&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a23de90&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a23f490&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a23ff50&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a23ef50&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5c452b90&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69e9bd10&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69e9a950&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5c441e50&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5d83fdd0&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5d83e9d0&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69f2ee90&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5d83d6d0&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5d83e1d0&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d83d650&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d83e810&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d83fcd0&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e199c33d0&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e197e65d0&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e19ae3190&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e199db990&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d8f1f10&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d8f1d10&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d8c2350&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d8f0bd0&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d8f0710&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d8e1e50&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d8f2190&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e18ced4d0&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a1635e290&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a16347710&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a1636bed0&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a257190&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a2af890&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a2ac650&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a2aebd0&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a2ad510&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a2adbd0&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a2ae4d0&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a2aeb10&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a2ae850&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69e931d0&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5c446690&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69d84690&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69f02a10&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5d822950&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5d820710&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69d66c90&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5d821c10&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5d821e50&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d822390&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d823e10&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5d821850&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f31850&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2eead90&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c28d0790&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c24e6690&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8a78910&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c8a78250&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8a7b010&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8a79190&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c8a79590&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c24960d0&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c28d13d0&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c8a7a590&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ef1b7950&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ef1e5710&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ef1802d0&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4ed3650&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ef1c8e50&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f4edc0d0&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed6d0910&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ecb4ed10&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ecb2e510&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4ed9e50&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ecb68a50&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ecb2e1d0&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a09bdc350&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a09c32550&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a09c31e10&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a0a23c550&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a09c31fd0&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a09c31950&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a09c324d0&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a09c312d0&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a09c31290&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a09c31710&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a09c311d0&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a09c302d0&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d8ab690&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d8c40d0&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0ce91090&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0ce72210&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0ce93090&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0ce90e10&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0ce5b250&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0ce92750&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0ce90f50&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0ce90ed0&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0ce92790&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0ce92890&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ef1593d0&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb56890&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ef18e690&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ef153650&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ed6eb950&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ed6e8290&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed6eb550&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed6e9190&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ed6e9b50&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed6ebc90&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed6e9090&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ed6e9110&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8c18450&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c247ad90&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c24c2c90&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2ee4810&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c24c35d0&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c24c3990&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c24c3950&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c24c38d0&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c24c3490&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c24c33d0&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c24c3310&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c24c3150&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5d7dbf10&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5f257450&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f6a053b10&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f6a042e90&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f6a053450&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f6a053c10&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f6a053290&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f6a053f10&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f6a0531d0&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5e35e050&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f6a053050&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f6a052c10&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f5e5ff410&gt;: [0.9541397518238303, 2.0361510612597575, 1.2049503382614706, 1.248722641999573, 1.6620255372232084, 0.9384491158342166, 0.8259456153867886, 1.2968255331018739, 1.261967724795004, 1.3195721001672194, 0.8640349758310877, 1.2347829872718985, 1.690197899564773, 0.9287735858072986, 1.2439806170206509, 0.8614684048602514, 1.17771489460581, 1.6970636288009442, 1.3017585546352894, 2.492793312076605], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f6a053bd0&gt;: [0.8742963007292982, 1.2386387444851845, 0.7754943635200456, 0.8057661214216914, 0.777132463002452, 0.8392697965483701, 0.8204045609454208, 0.8167007942212201, 0.8297945897378147, 0.8727087221930807, 0.8573766011427615, 0.8429345088740734, 0.8362070391599941, 0.8485891264507215, 0.8919736853335742, 0.8342816598205974, 0.8325266111078077, 0.8393096071324518, 0.8238515880466459, 0.8586951920678094], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2f69f25190&gt;: [0.8399970208688766, 0.840853188571298, 0.7907372743626849, 0.8123580926027346, 0.7798644912890544, 0.8288736952514962, 0.8135414184783267, 0.8031939782655029, 0.8055565233229659, 0.8722357318696193, 0.8391215400308721, 0.8559868648861213, 0.8220221144514662, 0.8239262609153806, 0.8554194430738276, 0.8437815947800001, 0.8157861456775135, 0.8230343138056934, 0.804819131004486, 0.8477939810455647], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69efe410&gt;: [2.2041083633565584, 1.2188324776930581, 3.56060503628066, 14.056578968960931, 2.419602953949064, 1.4838720995789902, 2.5713962311568204, 7.589699691739293, 1.1375388784491338, 2.815918953177762, 2.3343164187321412, 2.23340633873572, 4.404182080187171, 0.7428590455939683, 1.0638783348712721, 2.625651613181943, 0.9599835231090711, 1.0540383505290316, 1.3948380498479325, 2.539058603021016], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f5c4b2950&gt;: [1.0546224882938382, 1.2544754487641296, 0.8871949362245113, 0.9669493846893837, 1.290680769989923, 1.7796978528456155, 1.0076342286962854, 0.7237740993265822, 0.9524760776434616, 0.8744081436742575, 1.2100269208660495, 1.150780059081395, 0.9505955834986036, 0.7617399643037993, 1.0510713249233579, 1.559979283937102, 0.9180026716957951, 1.0100861134430634, 0.8941439514559691, 1.680239720680257], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2f69f1b690&gt;: [1.1965484472408432, 1.2840569561815995, 0.9032760215086878, 4.689347796417847, 0.8375803286421588, 0.913131682549355, 1.045495910472314, 0.7155319885287078, 1.0925812221471805, 0.9983375001453455, 1.1923070986751358, 1.468255594399925, 0.898245112378547, 0.7997670975860581, 2.8580375803343254, 2.1294323081102866, 0.8520146594332513, 1.3905548176558644, 1.2842701932199592, 1.7442412131514888], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69f1b3d0&gt;: [0.864814258002798, 0.9132476646053933, 0.7270486832517581, 0.7792367218286069, 0.7295567921422621, 0.7492958449502549, 0.7961991768990183, 0.7142347531125048, 0.7619193940584366, 0.7887016546553395, 0.8950909786199295, 0.7375040881961588, 0.7332730829311851, 0.7415638985602604, 0.8657987095777726, 0.8420546592892574, 0.8049564684815891, 0.8280481551032144, 0.7207415722844415, 0.8449874153427931], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f69f18f50&gt;: [0.9591356630506254, 0.9976117646227385, 0.9293726245730076, 0.888587957456008, 0.8916380051582832, 0.9332470307605508, 1.0194363528418715, 0.8926849510376781, 0.8956950459207508, 0.9610645097582545, 0.9189435477872556, 0.9748270070805508, 0.9181743415314181, 0.8957164328115231, 0.9184127822780755, 0.9498293318998743, 0.9316307706585614, 0.9845515329875175, 0.8677519089248769, 0.9769197499487026], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2f5c3e8990&gt;: [0.8779644692938323, 0.9037536052673764, 0.7519372439416786, 0.7940189371558342, 0.743232513806029, 0.7641162735227477, 0.7857041522681678, 0.701457737967986, 0.8168559941541272, 0.8607248072307363, 0.880805828928815, 0.7985859280755201, 0.7590789774630006, 0.7509331672279979, 0.8542777618786789, 0.8434117102762402, 0.8186725800763384, 0.841100207429731, 0.7810291688629002, 0.834290423598578], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c496250&gt;: [12.872733353256129, 18.45091780633378, 15.447280023907354, 16.30546224745776, 16.734553359232965, 14.16000668858174, 14.589097800356942, 11.585460017930515, 17.16364447100817, 16.734553359232965, 15.447280023907354, 17.592735582783373, 15.447280023907354, 16.30546224745776, 15.018188912132148, 18.021826694558577, 15.018188912132151, 17.16364447100817, 17.592735582783373, 15.876371135682556], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c3e9d50&gt;: [7.2732432890254515, 5.742003497616885, 4.726256232814615, 6.4563198262226615, 7.262187178884111, 3.516053024826529, 5.643602900407594, 3.0718605877481893, 5.631144611270343, 7.294573758897216, 4.433399692419509, 6.960458457754493, 6.489326834820754, 4.778571103703571, 6.031435251435184, 6.846174784831145, 3.2280234500041396, 6.919820125591865, 4.8136007198825626, 6.465973757368094], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2f5c3eb910&gt;: [4.052425174469036, 3.726117964047318, 2.36555081162648, 4.4888518355230955, 3.647941431999561, 2.3824845426709533, 1.5922044914378806, 1.5435180436483837, 3.6362648932732315, 3.2551476629395095, 1.9825454261716078, 2.916543485206474, 3.6588496549980634, 2.360385757071362, 2.775199608651072, 3.2079555319089486, 1.5699578186954497, 5.319432129936395, 2.3926244499416267, 3.2738216619622937]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c2f40790&gt;: [1.3059566162242722, 1.7126850807276506, 1.2551208730408547, 1.2666184067258328, 0.7881534723981202, 1.2948982681980472, 1.2175296451753759, 0.8119578919631123, 0.8974699732897239, 0.7822547361280835, 1.1722603032788739, 2.0312710677066916, 1.7374061866778914, 0.8781989828966513, 0.8367059512424504, 1.2837445774947507, 0.8503174355564191, 1.1969095037667439, 1.7445537720020685, 1.1782143054141436], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c24bb890&gt;: [0.8198165169304041, 0.8531187478439263, 0.8088326592664495, 0.7960543327491453, 0.7681642747454163, 0.8107506526533965, 0.8065249582336849, 0.7695613407926726, 0.7855387051552989, 0.7897610216753138, 0.7917396510207025, 0.798098185202163, 0.8360055620175958, 0.8551087343146926, 0.7734892539824832, 0.8074092968895903, 0.8037019280017407, 0.8195209212285325, 0.8218693039531735, 0.8231735771756457], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0c8bff190&gt;: [0.7948431867343921, 0.8242776844935003, 0.7867787560733448, 0.7955632651368868, 0.7490430633740839, 0.8011595952438737, 0.7915265567566088, 0.7884359489515734, 0.7876705752412282, 0.7872632054166346, 0.7647776719089643, 0.7865187656136341, 0.8288677454597223, 0.8445610163012376, 0.7752955591619942, 0.8202319951411499, 0.7993240022713168, 0.8188552458588567, 0.7992575177797517, 0.8089333813552854], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c2ed5990&gt;: [1.893896763702125, 1.506200334354735, 2.096540458211722, 1.4577068705467755, 4.5326012783667, 1.3354884434487917, 5.2540239583067825, 1.7534585472004434, 2.46018477889705, 3.830852051917479, 2.1666714382546552, 2.8663567707994897, 1.2284503759941465, 3.6946091023566043, 2.1960844281556864, 1.5729294373757237, 1.5432680848103888, 4.002019947411911, 2.3280558214312728, 3.2493180799613786], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c28b2350&gt;: [0.7937672317249698, 1.0894365441473528, 0.7489876206456962, 0.8476375206760351, 0.8020309924500834, 0.7845912034899479, 0.9427011576874627, 0.7834298323957583, 0.9031932769214082, 0.7650428145668224, 0.6659350565332653, 0.9406025227224794, 1.8271083417851537, 0.9609266067521054, 0.8110490827360118, 0.8107711424388382, 0.8503284320636475, 1.6878579882977616, 0.9117727389479559, 1.031213174070653], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0c24d1dd0&gt;: [0.7872454413042569, 4.5050369429464086, 3.775119802867548, 0.8940258666288203, 0.7957336826776917, 2.1787449226475264, 0.6666375836383294, 2.4945799369477704, 1.1921409231043982, 1.24291854651168, 0.6250251259153431, 2.672586213666174, 1.6487072806054002, 1.140863157518469, 0.9488687342603603, 0.8758601087860362, 1.191786293585236, 1.0456753719320406, 1.0758757677208979, 0.9872629019312552], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c24d3490&gt;: [0.7345147894934068, 0.8567020173430864, 0.741760050087696, 0.764283780232033, 0.7520360535255687, 0.6764057998486693, 0.6889898622277753, 0.714002862406881, 0.7192466476074854, 0.7040827150930623, 0.6744366533856462, 0.7885252566673547, 0.8113688432287719, 0.732368770177363, 0.7210526180152068, 0.7456101889152918, 0.6946484795056876, 0.7920032982421261, 0.6797469767831441, 0.7937096202542693], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c24d2250&gt;: [0.8968705516639055, 0.9676034543570544, 0.9303481099360675, 0.9231213833110636, 0.8427675835759244, 0.8717271768551048, 0.9274394851940386, 0.9235139367141715, 0.9559356463244226, 0.9584410610603429, 0.8894374520259964, 0.8724089554358133, 0.9761058333036454, 0.9881567744273383, 0.9628092311267051, 0.8942328852170731, 0.9030909285699783, 0.8597403217083543, 0.9591791419160132, 0.9572247774108585], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0c2ede790&gt;: [0.7772640440778469, 0.857987952015433, 0.8039671259354826, 0.7544244520136382, 0.7610611376458574, 0.7028063665372214, 0.7159366731251613, 0.7030556906163662, 0.7697477683258855, 0.7649339297875928, 0.6874111063132526, 0.8033974934593682, 0.8368026270304544, 0.7348567335195634, 0.7694224395260734, 0.8157442177729435, 0.7074759126331667, 0.8059070018976203, 0.7048158055250554, 0.8201680676141837], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f413d0&gt;: [16.73455335923297, 15.018188912132151, 15.447280023907354, 15.447280023907354, 18.880008918108985, 16.30546224745776, 15.447280023907354, 13.730915576806538, 18.880008918108985, 14.16000668858174, 14.589097800356942, 15.876371135682554, 15.018188912132148, 18.880008918108985, 15.447280023907354, 18.450917806333784, 16.305462247457765, 15.018188912132151, 15.447280023907354, 13.301824465031332], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f35210&gt;: [5.720673027745121, 5.202053499495139, 5.204857857486958, 3.94856892317854, 7.778002349142275, 4.766112814566322, 4.81702550645937, 4.37221264079604, 4.4285727268467925, 3.9519937097553477, 4.379062213949654, 6.856449144561568, 4.823254651027995, 5.290179736974008, 7.711988331946088, 6.48107508267123, 3.981575931776632, 6.906120979284639, 5.234440079508243, 4.769537601143129], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0c2f35550&gt;: [4.1114417313687674, 2.7902451845743945, 3.5702508760770466, 1.5930285565455224, 2.477030126558009, 2.3569609704945553, 3.1847926562958495, 1.1701800240220372, 1.6442370227242509, 2.3993261359524007, 2.371146092927024, 4.464231031534273, 2.4736053399812015, 3.2529771682157724, 2.816888596144114, 2.8774552191825955, 1.9906627258613832, 4.442752674519671, 2.399904249840667, 3.2425549213425118]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ecb37950&gt;: [2.077834294753519, 0.9520821106783541, 1.282101890078395, 1.3313907720371085, 0.8125337679664959, 1.172539921481997, 1.666657825186597, 1.6980774122335671, 0.7354425252620638, 2.5108284885469594, 1.6464382357948304, 0.8114278467708471, 1.318108417792215, 1.3067169400679366, 1.6443023750840027, 2.1486468810233736, 0.8113775401899617, 1.2393037764756583, 0.9058116253173893, 1.270089983769128], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ed6dda50&gt;: [1.2383363243298224, 0.8026797653720837, 0.8494640654210736, 1.2252806309661455, 0.8000345734568532, 1.1978773068422013, 0.8276078505896935, 0.8540485053632763, 0.7803420184555157, 0.8623442013383641, 0.8222557230921216, 0.8318554391791861, 0.8200261614623336, 0.8585823990311515, 0.8107810818923998, 0.8154114934162024, 0.809205451926936, 1.202782843509412, 0.8095056068109221, 0.868571308151352], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f02ed6f8b50&gt;: [0.8225363815033235, 0.8029051223821555, 0.849284290385087, 0.8824418252320043, 0.807084594079265, 0.8000553707739442, 0.8004889596804796, 0.8412243338139062, 0.7726548364539931, 0.8397436809297794, 0.8075553687513038, 0.8061282086083194, 0.8310336286145314, 0.8378894703556276, 0.8292112419785359, 0.8279602052113627, 0.8064197196998254, 0.8219485459358719, 0.8039723093680531, 0.8506887328739341], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02f7383650&gt;: [1.9239968416355475, 2.471349631887229, 2.357000251781133, 1.3095263045804433, 0.8723466311015405, 7.852468629804912, 0.9520774832746607, 4.509479219265307, 0.9705314419942755, 12.024125208835487, 10.174653136658335, 1.4035385637395876, 1.1878350362080283, 9.430463958583031, 0.9879213648422164, 1.7733000373381465, 9.168703992444785, 0.8698120860265152, 0.8034086995527596, 0.8777939353977894], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ef185650&gt;: [0.7243676710255242, 0.773313734127749, 2.9768305119831604, 1.2441304815709309, 1.0200792500673785, 2.6640995989781517, 0.9651936409436969, 0.9717205777264697, 0.7371428777986255, 0.755943197529539, 0.7583887993988656, 2.2014555362073076, 0.7512560010273402, 1.0595897443152262, 1.052847364814579, 2.0925481864869266, 0.862463362798468, 0.9305676345893309, 3.3183216154986233, 0.8901871452471857], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f02ef1b9dd0&gt;: [3.3879961525656275, 2.1816572819268023, 0.989065783438164, 2.0895188992990796, 2.130578148594669, 1.0747419467393466, 0.9755095438266862, 0.9592415111170157, 0.7414002169317101, 1.3170687775918217, 0.7829729955245478, 0.937964782798974, 0.7363402503848013, 1.0130369532270853, 1.8745311873650836, 1.498723096019183, 2.115694882773438, 0.8601500975470845, 2.3399367262268336, 1.1746042290418681], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ef1bb910&gt;: [0.7523701269164111, 0.7243390213137304, 0.7643824719338641, 0.8973593556833528, 0.7860317122234299, 0.7353213048902523, 0.7781566909898181, 0.7442097723055303, 0.6877572599713726, 0.7043918421296992, 0.7657716103497397, 0.7755006379378093, 0.786881131725113, 0.7318081755469759, 0.8603378788412156, 0.6960064519452185, 0.8058352378771219, 0.7201055784340503, 0.691341623375244, 0.7726582136424087], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ef1bbf10&gt;: [0.9307794748776528, 0.9458504249308132, 0.9765711229475774, 1.0282129474623747, 0.9715668762588046, 0.9999630803379767, 0.972306108482587, 1.0090368939260614, 0.9724990747733447, 1.009363879912735, 0.9200170933330909, 1.0108651575874692, 0.9757898949641506, 0.9737830548512553, 0.9599391197349273, 0.8985202958266234, 0.9684960114123582, 1.0056310863209212, 0.9877978686804657, 0.9378063561862785], &lt;method-wrapper \'__str__\' of SVC object at 0x7f02ef1bb5d0&gt;: [0.8143059546196687, 0.701693118564355, 0.8181791890694085, 0.9110615953179471, 0.8119891842043578, 0.7963188489400006, 0.7916185162997474, 0.7698173731001661, 0.7137319375081516, 0.7656185002726155, 0.8037555946094354, 0.7759496044672151, 0.8003711082292506, 0.7449048229297678, 0.8740381671594716, 0.7201306115515487, 0.8176822090219525, 0.7082041543881434, 0.7045589425842783, 0.797283650315202], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4e81e50&gt;: [18.45091780633378, 15.87637113568256, 12.872733353256127, 17.592735582783376, 16.734553359232965, 15.44728002390735, 14.589097800356948, 14.160006688581742, 13.301824465031334, 16.73455335923297, 16.734553359232965, 13.730915576806538, 17.16364447100817, 16.30546224745776, 15.87637113568256, 14.589097800356946, 17.592735582783373, 17.16364447100817, 16.73455335923296, 16.305462247457765], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02f4e98a50&gt;: [6.08437055090913, 3.16605464796975, 2.728091355460034, 9.019189958147555, 6.503187302953912, 6.067867046610083, 6.954229313185867, 5.277101019251768, 4.414873580539565, 5.680034695582494, 4.815002898878472, 4.010537725212931, 4.929907000386807, 6.85100175040386, 3.5979501177367723, 3.980955503191644, 3.9713015720462117, 5.6504524735612085, 3.977530716614838, 4.398990504825507], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f02ef1b9ed0&gt;: [1.1793345443591354, 2.014015803314044, 2.002339264587713, 4.137937255795648, 4.107586718046534, 2.875271289775765, 4.1050781343403955, 2.523115852878341, 0.8382775322997744, 3.702764886594658, 3.266190338397759, 1.611850442711146, 3.2509545606348746, 2.826690414432387, 2.773311453529921, 2.8203133827209217, 1.9769501448710631, 2.82485800869105, 1.9962580071619282, 2.843666460173582]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a09c30fd0&gt;: [2.942348997433789, 1.731910723824185, 1.269472276583604, 1.2747406656999567, 1.6462988240507355, 2.54091012137658, 1.2288765703180498, 0.9819174810882464, 0.7881166005003275, 2.0454512308548125, 0.8857381686981605, 1.243837689162159, 0.7933185269532376, 1.2604806052053001, 0.8691294031533472, 1.6759129586854669, 1.28182723115962, 1.6486505617007086, 0.851605877907817, 1.6763535875141695], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a16315950&gt;: [0.8691341576987481, 0.8753903908489514, 1.2245870250963444, 0.8559904792860008, 0.8223956853141933, 0.8819413087743199, 0.8160933264591986, 0.8966785336010713, 0.8126924294040553, 0.8788330138385101, 0.8392693915412499, 0.8446731233072396, 0.7845033680232347, 0.8864225825651934, 0.812998314775005, 0.8274381225261987, 0.8507216249035816, 0.8644652345872965, 0.8319094620537066, 0.8418362998772493], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f1a16351650&gt;: [0.8464013149271552, 0.8538668534095616, 0.8364597303171072, 0.8305180662346117, 0.8387615974330674, 0.8745544606530021, 0.8067276663130881, 0.8759659671112855, 0.8098200713344121, 0.8586673405445067, 0.8174233184540173, 0.8175792374254042, 0.7946917176877797, 0.8643739371554008, 0.7976912830323903, 0.8117195658677161, 0.8329194994968896, 0.8445479575046462, 0.7997496649137213, 0.8309538299812399], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f19f8757190&gt;: [2.2744460726660556, 4.782901508950912, 3.2473669361100534, 8.08100140183167, 1.9062774473088335, 4.493122524010274, 8.602840651590641, 1.8786920250725738, 1.468286054384072, 4.637689566128855, 2.3038250235253805, 5.420144329064726, 5.69538423734469, 3.0679975302831197, 1.8642493208899649, 4.800992372501658, 9.839982689093171, 4.698762027720418, 8.17015873839184, 1.1715917098667235], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a1635dcd0&gt;: [0.9900693612499984, 1.2501675588837906, 1.1383712537187858, 0.7319030870387006, 1.0348749851413825, 0.7644994994639648, 1.0983692748158198, 1.0054190061006545, 0.9971324399330932, 0.8827821048386758, 0.956117905645788, 1.1241134236901473, 0.8944361928841642, 1.1153642623244298, 0.9204045437505163, 0.9461098600069533, 1.1513873862585866, 1.5312290041917507, 2.305723735475806, 1.2049677052001964], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f1a1635d790&gt;: [6.109303923950584, 1.5347547839010773, 1.7838470715787682, 0.7900238004564907, 0.9390718915683985, 0.7654648445395301, 1.2554451432490705, 2.856820138705886, 1.3014604592661676, 0.933524969834538, 1.1691006432504347, 1.2009257982476587, 2.088882219209688, 1.3415413049093754, 1.0755502525478469, 1.4673763420039942, 1.0722711355432542, 1.0626319267524407, 4.039354995354309, 1.8192445575222376], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a1635fe10&gt;: [0.8477287723493943, 0.8724366170506053, 0.7876389814530149, 0.6874839606706121, 0.790634028858196, 0.7637748144092198, 0.8069571093452697, 0.8606745481485489, 0.8439545598648069, 0.7442402661525073, 0.7909999960747759, 0.8818342633195266, 0.75345986410353, 0.8447979996850327, 0.8253973010838676, 0.8322287177066536, 0.8086002123558041, 0.8423344461297023, 0.7714943434604935, 0.8858749591065017], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a1635f3d0&gt;: [0.9929588206910909, 0.9812799927055904, 0.9780280496389121, 0.9732559828257857, 0.94843609111966, 1.0157616966333298, 0.9993629000670309, 0.9390903771481645, 0.9835947659408942, 0.98840463045035, 0.9330806912041871, 0.9654129196067261, 0.9859189468394275, 0.9410033768699536, 0.9519203579583762, 0.9761760723826911, 0.9613271758646156, 0.9377151293704232, 0.9467407618220365, 0.9655613091100397], &lt;method-wrapper \'__str__\' of SVC object at 0x7f1a0a295550&gt;: [0.8358848867091934, 0.9009044600667864, 0.837403179696105, 0.7000212654000104, 0.8166593320511033, 0.7653338428484159, 0.8086783716103036, 0.9317691210140673, 0.85621343484865, 0.7704309304625442, 0.7794388136447917, 0.9066521127965285, 0.7547525011508399, 0.8684134435259809, 0.8288923540785543, 0.8449142186965604, 0.8677950313976203, 0.8966151312650038, 0.808803341093425, 0.8861216888969433], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a296a10&gt;: [17.16364447100817, 19.738191141659396, 16.305462247457758, 13.730915576806535, 18.02182669455858, 16.305462247457758, 18.45091780633378, 17.16364447100817, 18.021826694558577, 15.87637113568256, 18.45091780633378, 17.592735582783376, 16.305462247457765, 16.30546224745776, 15.447280023907354, 17.592735582783376, 18.02182669455858, 17.592735582783373, 19.309100029884192, 18.021826694558577], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a295ed0&gt;: [6.5154842702652305, 5.676609909005687, 6.158636320254838, 5.207041786893788, 5.725499993317838, 5.234440079508244, 6.557524781423767, 6.8819861514210565, 6.533389953560187, 2.792082765075322, 8.136872906733563, 6.541021277124723, 6.508634697111616, 5.669760335852073, 7.268416323452737, 4.857043410037008, 4.461579735444884, 5.708996489018792, 4.8610886251988035, 7.761498844843229], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f1a0a296090&gt;: [3.6942307948425475, 3.6672492942904262, 3.264505819799263, 2.39064415705745, 3.339891428538293, 4.037796390608047, 2.411488650803971, 4.085284295924289, 2.0403211259013623, 1.999534906595895, 4.4680860448565065, 3.7135252224503197, 3.2707349643678882, 3.2802544430535736, 2.8184252275997714, 2.8550606592973238, 2.4482162202645514, 3.2615670093476967, 2.81458364896063, 4.462356311096215]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0ce8b190&gt;: [1.2670401580725146, 1.6974093984671577, 1.6694064337986012, 1.329368164456211, 1.6889485669960511, 0.8919227606851812, 1.3413746279665493, 1.3507773374079064, 1.6712883514058898, 1.336999488020746, 1.2514159847463442, 1.183249866793862, 1.2624743327725694, 1.7072376865699461, 0.8338926343373061, 1.2422034771445478, 1.6864539014875863, 1.6828834656528229, 1.3873547818407626, 2.1525158125432813], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d283990&gt;: [0.8226379084909725, 1.2576864111925978, 0.8379694016596841, 0.8448446085711494, 0.7983736881988328, 0.8205776342210032, 0.850849068072485, 0.8630892960552288, 0.8199198049466092, 0.8614195413717034, 0.7853646890820054, 1.188047561847462, 1.2304889298844668, 0.8133753183706105, 0.8241370831868506, 0.8469471142697439, 0.8285318105529391, 0.8697221709288069, 0.8484168665978219, 0.8400975303976946], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7e0d9361d0&gt;: [0.8240971688349263, 0.8485247955497603, 0.829989879746457, 0.8418318728766914, 0.8081774481887138, 0.828444237196176, 0.8401725837392039, 0.8368521397419312, 0.8014429590433833, 0.833450691094623, 0.7939311641624895, 0.8216601358744998, 0.8383245972706722, 0.8048392642724764, 0.8142642835320767, 0.8494980441363081, 0.8246158520852773, 0.8354130810174997, 0.8377413245530954, 0.8390380953972784], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d2813d0&gt;: [2.1526550491052783, 6.248281338854271, 10.316973158702078, 1.8433567430213122, 2.6900150661853837, 1.852381941882784, 2.86837103847346, 2.1835814649027454, 2.190984971319107, 0.8905115827274235, 1.853940740013745, 2.611986994510589, 5.074968122241798, 1.7521212637515908, 3.040063662256425, 5.527993041437471, 7.32124145449428, 2.2409757321546593, 2.0749170503471976, 2.5365234627112794], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0ecd3690&gt;: [1.4176239954835632, 1.2698881156717823, 1.3870678017654758, 1.1934034679563257, 1.5183565594511248, 1.276090645774438, 1.1677866823315475, 1.0006357427202868, 3.28425296170099, 2.5231858885334852, 1.160828344631002, 0.9303097041164166, 2.1804372053581953, 1.413969461416824, 1.445799644686011, 1.0521203864411555, 1.325467070721476, 1.0894720319058284, 1.498536717871281, 1.9574739609870138], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7e0d8f5510&gt;: [2.753636870572277, 1.3534867189319117, 1.0587111930191104, 0.9194986128904632, 0.8289797678010411, 1.131776216102393, 0.9723526644198829, 0.9943935334027052, 0.8557271594300604, 1.4071020827592309, 0.9942339068282864, 1.5451487835210138, 1.7494466705587368, 0.8295916026150084, 0.9422235631729527, 1.8091042336475027, 1.1124470189789206, 1.428178389516395, 1.4602577038314588, 0.9968786023131339], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d8f7c50&gt;: [0.9053801578726447, 0.8158472460763724, 0.8698999632970734, 0.8266490720422084, 0.7874493108708647, 0.8781355044643616, 0.8761039499662931, 0.6968597719253777, 0.796164744909815, 0.8291546266428811, 0.7463489155326328, 0.7580545856253945, 0.7692280315311909, 0.814028959623626, 0.7686277189189112, 0.8488611658059377, 0.9004529500649952, 0.8699053383145537, 0.866570421171544, 0.8449232820825736], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d8f4710&gt;: [0.9822524795967764, 0.9788088408740497, 0.9754634518825523, 1.0034263739626959, 0.9739262981227942, 0.9404291945300332, 0.9282638371712405, 0.9855958768858799, 0.9500676283155153, 0.9738132586727937, 0.9602471746432999, 0.9751075776278109, 0.9747113436099225, 0.9633787883620896, 0.9103971403804597, 0.9764886059567432, 0.9724398534557468, 0.9530242096643794, 0.9949023220115675, 1.0325203017286697], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7e0d8f4390&gt;: [0.9061808954904906, 0.8402192762854084, 0.9079182692986715, 0.8391702794377673, 0.7650576465723641, 0.8907098858350166, 0.9022173396077369, 0.7457391984388821, 0.7867425180005336, 0.8432705107924793, 0.7836983370979531, 0.7824472307795615, 0.8197217719983724, 0.8269052734958054, 0.771869917982748, 0.8986362730912506, 0.9377206730237291, 0.9184520482378188, 0.8911359116370351, 0.8700738664208504], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d259e50&gt;: [17.592735582783373, 18.45091780633378, 18.880008918108985, 18.02182669455858, 17.592735582783373, 17.16364447100817, 19.738191141659396, 18.880008918108985, 16.30546224745776, 15.876371135682556, 17.16364447100817, 17.16364447100817, 15.87637113568256, 17.592735582783376, 18.450917806333784, 18.021826694558577, 18.021826694558577, 19.309100029884192, 17.592735582783376, 15.018188912132148], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0cea8a50&gt;: [5.653877260138015, 7.789058459283616, 9.001904703437589, 8.55428747978244, 4.420320974697269, 7.366816920662025, 6.923244912168673, 6.893042261562399, 4.02221426393926, 3.946546315597643, 5.267447088106337, 5.669760335852073, 5.678012088001596, 6.50520991053481, 6.992845037767599, 7.353738202939786, 5.682839053574313, 6.492131192812572, 7.782047564304068, 4.447880589137658], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7e0d8f7690&gt;: [3.3040377472516615, 2.8675189484345758, 5.732922505600127, 4.53261917997685, 1.632264709712241, 3.7083601678952025, 3.3028257700953128, 3.209400025601579, 2.051081461757024, 2.7294096566164194, 2.876673468771674, 3.6601039468511325, 2.012465737175294, 3.2322671269289973, 1.6383459671380263, 4.068646339165495, 3.673668640698613, 2.467228308269736, 4.974746694777572, 2.0488975323501935]}'}</t>
-  </si>
-  <si>
     <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
+    <t>{0: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 1: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 2: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 3: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 4: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
     <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
@@ -235,34 +214,31 @@
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 1: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 2: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 3: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 4: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 1: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 2: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 3: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 4: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
@@ -699,40 +675,40 @@
         <v>48</v>
       </c>
       <c r="F2">
-        <v>0.8573451602863369</v>
+        <v>0.930976430976431</v>
       </c>
       <c r="G2">
-        <v>0.071431833054382</v>
+        <v>0.02912019974469988</v>
       </c>
       <c r="H2">
-        <v>0.6333333333333334</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I2">
-        <v>0.07766431633476234</v>
+        <v>0.09805362039035236</v>
       </c>
       <c r="J2">
-        <v>0.5585278555866792</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="K2">
-        <v>0.136227571680221</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="L2">
-        <v>0.6487446248563318</v>
+        <v>0.6223184223184223</v>
       </c>
       <c r="M2">
-        <v>0.2398420917618662</v>
+        <v>0.2521475266572068</v>
       </c>
       <c r="N2">
-        <v>0.5585278555866792</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="O2">
-        <v>0.136227571680221</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="P2">
-        <v>0.5673176308315095</v>
+        <v>0.6263221817169187</v>
       </c>
       <c r="Q2">
-        <v>0.1833411503695693</v>
+        <v>0.2287779105280338</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
@@ -749,43 +725,43 @@
         <v>48</v>
       </c>
       <c r="F3">
-        <v>0.8560016599232286</v>
+        <v>0.9299663299663299</v>
       </c>
       <c r="G3">
-        <v>0.06854922149677943</v>
+        <v>0.03008903112828135</v>
       </c>
       <c r="H3">
-        <v>0.6428571428571428</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="I3">
-        <v>0.1010152544552211</v>
+        <v>0.09331389496316866</v>
       </c>
       <c r="J3">
-        <v>0.5851045468692527</v>
+        <v>0.6552188552188551</v>
       </c>
       <c r="K3">
-        <v>0.1543493410032004</v>
+        <v>0.1957917524334013</v>
       </c>
       <c r="L3">
-        <v>0.6492673531978956</v>
+        <v>0.628968253968254</v>
       </c>
       <c r="M3">
-        <v>0.244210052277187</v>
+        <v>0.2553348647797313</v>
       </c>
       <c r="N3">
-        <v>0.5851045468692527</v>
+        <v>0.6552188552188551</v>
       </c>
       <c r="O3">
-        <v>0.1543493410032004</v>
+        <v>0.1957917524334013</v>
       </c>
       <c r="P3">
-        <v>0.5938957146650199</v>
+        <v>0.6324534001243518</v>
       </c>
       <c r="Q3">
-        <v>0.2015561811262448</v>
+        <v>0.231881191679186</v>
       </c>
       <c r="R3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -799,43 +775,43 @@
         <v>48</v>
       </c>
       <c r="F4">
-        <v>0.8542351620782993</v>
+        <v>0.9296296296296296</v>
       </c>
       <c r="G4">
-        <v>0.07209859173173598</v>
+        <v>0.03036656265558114</v>
       </c>
       <c r="H4">
-        <v>0.6523809523809524</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="I4">
-        <v>0.09594972228385659</v>
+        <v>0.09331389496316866</v>
       </c>
       <c r="J4">
-        <v>0.5911651529298588</v>
+        <v>0.6552188552188551</v>
       </c>
       <c r="K4">
-        <v>0.1547144784450038</v>
+        <v>0.1957917524334013</v>
       </c>
       <c r="L4">
-        <v>0.6578387817693243</v>
+        <v>0.628968253968254</v>
       </c>
       <c r="M4">
-        <v>0.2462495977554722</v>
+        <v>0.2553348647797313</v>
       </c>
       <c r="N4">
-        <v>0.5911651529298588</v>
+        <v>0.6552188552188551</v>
       </c>
       <c r="O4">
-        <v>0.1547144784450038</v>
+        <v>0.1957917524334013</v>
       </c>
       <c r="P4">
-        <v>0.5994263168852773</v>
+        <v>0.6324534001243518</v>
       </c>
       <c r="Q4">
-        <v>0.2025169227007157</v>
+        <v>0.231881191679186</v>
       </c>
       <c r="R4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -849,43 +825,43 @@
         <v>48</v>
       </c>
       <c r="F5">
-        <v>0.8524413132256271</v>
+        <v>0.9282828282828282</v>
       </c>
       <c r="G5">
-        <v>0.06810613480208683</v>
+        <v>0.02611544704332027</v>
       </c>
       <c r="H5">
-        <v>0.6428571428571429</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I5">
-        <v>0.09159706696033973</v>
+        <v>0.09805362039035236</v>
       </c>
       <c r="J5">
-        <v>0.5856845768610474</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="K5">
-        <v>0.1508415340394001</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="L5">
-        <v>0.6512571888658846</v>
+        <v>0.6223184223184223</v>
       </c>
       <c r="M5">
-        <v>0.2432432365356274</v>
+        <v>0.2521475266572068</v>
       </c>
       <c r="N5">
-        <v>0.5856845768610474</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="O5">
-        <v>0.1508415340394001</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="P5">
-        <v>0.5958686287753873</v>
+        <v>0.6263221817169187</v>
       </c>
       <c r="Q5">
-        <v>0.1994803104502262</v>
+        <v>0.2287779105280338</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -899,43 +875,43 @@
         <v>48</v>
       </c>
       <c r="F6">
-        <v>0.8516372879117977</v>
+        <v>0.9282828282828282</v>
       </c>
       <c r="G6">
-        <v>0.07003059117977109</v>
+        <v>0.02611544704332027</v>
       </c>
       <c r="H6">
-        <v>0.6476190476190476</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I6">
-        <v>0.09689042833036095</v>
+        <v>0.09805362039035236</v>
       </c>
       <c r="J6">
-        <v>0.5893882805647511</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="K6">
-        <v>0.1541448639878063</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="L6">
-        <v>0.6542907211193656</v>
+        <v>0.6223184223184223</v>
       </c>
       <c r="M6">
-        <v>0.2454067731765016</v>
+        <v>0.2521475266572068</v>
       </c>
       <c r="N6">
-        <v>0.5893882805647511</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="O6">
-        <v>0.1541448639878063</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="P6">
-        <v>0.5994783959145661</v>
+        <v>0.6263221817169187</v>
       </c>
       <c r="Q6">
-        <v>0.2024470254361118</v>
+        <v>0.2287779105280338</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -949,43 +925,43 @@
         <v>48</v>
       </c>
       <c r="F7">
-        <v>0.8510839015740977</v>
+        <v>0.9282828282828282</v>
       </c>
       <c r="G7">
-        <v>0.06998895618507756</v>
+        <v>0.02611544704332027</v>
       </c>
       <c r="H7">
-        <v>0.6428571428571428</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I7">
-        <v>0.1096272803163937</v>
+        <v>0.09805362039035236</v>
       </c>
       <c r="J7">
-        <v>0.5852488470135528</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="K7">
-        <v>0.1578474542067641</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="L7">
-        <v>0.6493767398801724</v>
+        <v>0.6223184223184223</v>
       </c>
       <c r="M7">
-        <v>0.2463385615663209</v>
+        <v>0.2521475266572068</v>
       </c>
       <c r="N7">
-        <v>0.5852488470135528</v>
+        <v>0.6491582491582492</v>
       </c>
       <c r="O7">
-        <v>0.1578474542067641</v>
+        <v>0.1928725802613405</v>
       </c>
       <c r="P7">
-        <v>0.5944546076688934</v>
+        <v>0.6263221817169187</v>
       </c>
       <c r="Q7">
-        <v>0.2043316678727513</v>
+        <v>0.2287779105280338</v>
       </c>
       <c r="R7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -999,43 +975,43 @@
         <v>48</v>
       </c>
       <c r="F8">
-        <v>0.849260815437286</v>
+        <v>0.9255892255892256</v>
       </c>
       <c r="G8">
-        <v>0.070174307018286</v>
+        <v>0.03367676700350169</v>
       </c>
       <c r="H8">
-        <v>0.6476190476190476</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I8">
-        <v>0.09689042833036095</v>
+        <v>0.09805362039035236</v>
       </c>
       <c r="J8">
-        <v>0.5897504456327985</v>
+        <v>0.6478114478114477</v>
       </c>
       <c r="K8">
-        <v>0.1521765113137998</v>
+        <v>0.1923216289816124</v>
       </c>
       <c r="L8">
-        <v>0.688780998389694</v>
+        <v>0.621978021978022</v>
       </c>
       <c r="M8">
-        <v>0.1815380495291991</v>
+        <v>0.2520021695709452</v>
       </c>
       <c r="N8">
-        <v>0.5897504456327985</v>
+        <v>0.6478114478114477</v>
       </c>
       <c r="O8">
-        <v>0.1521765113137998</v>
+        <v>0.1923216289816124</v>
       </c>
       <c r="P8">
-        <v>0.6054436972528283</v>
+        <v>0.6246386800334169</v>
       </c>
       <c r="Q8">
-        <v>0.1905795273488173</v>
+        <v>0.2280338385389016</v>
       </c>
       <c r="R8" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1049,43 +1025,43 @@
         <v>48</v>
       </c>
       <c r="F9">
-        <v>0.8453404257325825</v>
+        <v>0.9255892255892256</v>
       </c>
       <c r="G9">
-        <v>0.06817292417903037</v>
+        <v>0.03511059708075073</v>
       </c>
       <c r="H9">
-        <v>0.6571428571428571</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I9">
-        <v>0.09712418121129111</v>
+        <v>0.09805362039035236</v>
       </c>
       <c r="J9">
-        <v>0.5973757179639533</v>
+        <v>0.6478114478114477</v>
       </c>
       <c r="K9">
-        <v>0.1493617246093235</v>
+        <v>0.1923216289816124</v>
       </c>
       <c r="L9">
-        <v>0.7036228787315744</v>
+        <v>0.621978021978022</v>
       </c>
       <c r="M9">
-        <v>0.1612984099303944</v>
+        <v>0.2520021695709452</v>
       </c>
       <c r="N9">
-        <v>0.5973757179639533</v>
+        <v>0.6478114478114477</v>
       </c>
       <c r="O9">
-        <v>0.1493617246093235</v>
+        <v>0.1923216289816124</v>
       </c>
       <c r="P9">
-        <v>0.6161547997100634</v>
+        <v>0.6246386800334169</v>
       </c>
       <c r="Q9">
-        <v>0.1812782259913005</v>
+        <v>0.2280338385389016</v>
       </c>
       <c r="R9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1099,43 +1075,43 @@
         <v>48</v>
       </c>
       <c r="F10">
-        <v>0.8451166661950975</v>
+        <v>0.9249158249158249</v>
       </c>
       <c r="G10">
-        <v>0.0680642883185576</v>
+        <v>0.03561073669257443</v>
       </c>
       <c r="H10">
-        <v>0.6571428571428571</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I10">
-        <v>0.09712418121129111</v>
+        <v>0.09805362039035236</v>
       </c>
       <c r="J10">
-        <v>0.5973757179639533</v>
+        <v>0.6464646464646464</v>
       </c>
       <c r="K10">
-        <v>0.1493617246093235</v>
+        <v>0.1918069256376231</v>
       </c>
       <c r="L10">
-        <v>0.7036228787315744</v>
+        <v>0.6228571428571429</v>
       </c>
       <c r="M10">
-        <v>0.1612984099303944</v>
+        <v>0.2523811520414504</v>
       </c>
       <c r="N10">
-        <v>0.5973757179639533</v>
+        <v>0.6464646464646464</v>
       </c>
       <c r="O10">
-        <v>0.1493617246093235</v>
+        <v>0.1918069256376231</v>
       </c>
       <c r="P10">
-        <v>0.6161547997100634</v>
+        <v>0.6215861769809139</v>
       </c>
       <c r="Q10">
-        <v>0.1812782259913005</v>
+        <v>0.2268059842630198</v>
       </c>
       <c r="R10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1149,43 +1125,43 @@
         <v>48</v>
       </c>
       <c r="F11">
-        <v>0.8449848626319214</v>
+        <v>0.9222222222222222</v>
       </c>
       <c r="G11">
-        <v>0.06792450608973603</v>
+        <v>0.03641037026849355</v>
       </c>
       <c r="H11">
-        <v>0.6523809523809524</v>
+        <v>0.7047619047619047</v>
       </c>
       <c r="I11">
-        <v>0.09110060223670945</v>
+        <v>0.09233675918888244</v>
       </c>
       <c r="J11">
-        <v>0.5936720142602495</v>
+        <v>0.6585858585858586</v>
       </c>
       <c r="K11">
-        <v>0.1457499309893935</v>
+        <v>0.1977162174954959</v>
       </c>
       <c r="L11">
-        <v>0.700789545398241</v>
+        <v>0.6526610644257703</v>
       </c>
       <c r="M11">
-        <v>0.1587331304177522</v>
+        <v>0.2717252073355572</v>
       </c>
       <c r="N11">
-        <v>0.5936720142602495</v>
+        <v>0.6585858585858586</v>
       </c>
       <c r="O11">
-        <v>0.1457499309893935</v>
+        <v>0.1977162174954959</v>
       </c>
       <c r="P11">
-        <v>0.6124998357481941</v>
+        <v>0.6325751879699248</v>
       </c>
       <c r="Q11">
-        <v>0.1779250804513027</v>
+        <v>0.2319489798766075</v>
       </c>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1193,49 +1169,49 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
       </c>
       <c r="F12">
-        <v>0.8423021060275963</v>
+        <v>0.905050505050505</v>
       </c>
       <c r="G12">
-        <v>0.08272413470684031</v>
+        <v>0.0409004300042026</v>
       </c>
       <c r="H12">
-        <v>0.6142857142857143</v>
+        <v>0.6761904761904762</v>
       </c>
       <c r="I12">
-        <v>0.07284313590846837</v>
+        <v>0.06998542122237651</v>
       </c>
       <c r="J12">
-        <v>0.5513213366154542</v>
+        <v>0.6430976430976431</v>
       </c>
       <c r="K12">
-        <v>0.1158243291152566</v>
+        <v>0.1648525560114348</v>
       </c>
       <c r="L12">
-        <v>0.6750503531556162</v>
+        <v>0.6697431223747013</v>
       </c>
       <c r="M12">
-        <v>0.1334788085204309</v>
+        <v>0.1452889408032716</v>
       </c>
       <c r="N12">
-        <v>0.5513213366154542</v>
+        <v>0.6430976430976431</v>
       </c>
       <c r="O12">
-        <v>0.1158243291152566</v>
+        <v>0.1648525560114348</v>
       </c>
       <c r="P12">
-        <v>0.5751550467150855</v>
+        <v>0.632849466532331</v>
       </c>
       <c r="Q12">
-        <v>0.1303330990352297</v>
+        <v>0.1788430450669794</v>
       </c>
       <c r="R12" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1243,49 +1219,49 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="F13">
-        <v>0.8339678295560649</v>
+        <v>0.9043771043771043</v>
       </c>
       <c r="G13">
-        <v>0.09002642530099234</v>
+        <v>0.04137990975282753</v>
       </c>
       <c r="H13">
-        <v>0.6238095238095238</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I13">
-        <v>0.07284313590846836</v>
+        <v>0.06023386019368343</v>
       </c>
       <c r="J13">
-        <v>0.576936026936027</v>
+        <v>0.6370370370370371</v>
       </c>
       <c r="K13">
-        <v>0.1258777057728109</v>
+        <v>0.1586198109301095</v>
       </c>
       <c r="L13">
-        <v>0.6792341446727412</v>
+        <v>0.6603414129729919</v>
       </c>
       <c r="M13">
-        <v>0.1343152617788068</v>
+        <v>0.134491347916901</v>
       </c>
       <c r="N13">
-        <v>0.576936026936027</v>
+        <v>0.6370370370370371</v>
       </c>
       <c r="O13">
-        <v>0.1258777057728109</v>
+        <v>0.1586198109301095</v>
       </c>
       <c r="P13">
-        <v>0.600674381050321</v>
+        <v>0.6267383554212198</v>
       </c>
       <c r="Q13">
-        <v>0.1417256994633832</v>
+        <v>0.1726837038692492</v>
       </c>
       <c r="R13" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1293,49 +1269,49 @@
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
         <v>48</v>
       </c>
       <c r="F14">
-        <v>0.8326797385620915</v>
+        <v>0.904040404040404</v>
       </c>
       <c r="G14">
-        <v>0.09213582913174828</v>
+        <v>0.0397106609586344</v>
       </c>
       <c r="H14">
-        <v>0.6380952380952382</v>
+        <v>0.6761904761904762</v>
       </c>
       <c r="I14">
-        <v>0.08702698515474791</v>
+        <v>0.04665694748158435</v>
       </c>
       <c r="J14">
-        <v>0.5873511020569844</v>
+        <v>0.6430976430976431</v>
       </c>
       <c r="K14">
-        <v>0.1351463501133482</v>
+        <v>0.1612228660109944</v>
       </c>
       <c r="L14">
-        <v>0.6882121971595655</v>
+        <v>0.6672400698716487</v>
       </c>
       <c r="M14">
-        <v>0.1414850353973503</v>
+        <v>0.1369263260267277</v>
       </c>
       <c r="N14">
-        <v>0.5873511020569844</v>
+        <v>0.6430976430976431</v>
       </c>
       <c r="O14">
-        <v>0.1351463501133482</v>
+        <v>0.1612228660109944</v>
       </c>
       <c r="P14">
-        <v>0.6118790831715838</v>
+        <v>0.6325638740344622</v>
       </c>
       <c r="Q14">
-        <v>0.1512802077150519</v>
+        <v>0.1752955437709423</v>
       </c>
       <c r="R14" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1343,49 +1319,49 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="F15">
-        <v>0.8304310613134142</v>
+        <v>0.9037037037037038</v>
       </c>
       <c r="G15">
-        <v>0.08310314226973067</v>
+        <v>0.04274105425762929</v>
       </c>
       <c r="H15">
-        <v>0.6285714285714287</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I15">
-        <v>0.0761904761904762</v>
+        <v>0.07737179432986628</v>
       </c>
       <c r="J15">
-        <v>0.5801106301106301</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="K15">
-        <v>0.1283433847986758</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="L15">
-        <v>0.6820847054180388</v>
+        <v>0.6768138294454085</v>
       </c>
       <c r="M15">
-        <v>0.1363690220207923</v>
+        <v>0.1520601981174081</v>
       </c>
       <c r="N15">
-        <v>0.5801106301106301</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="O15">
-        <v>0.1283433847986758</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="P15">
-        <v>0.6040077143836543</v>
+        <v>0.6398366314142327</v>
       </c>
       <c r="Q15">
-        <v>0.1443254175911664</v>
+        <v>0.1857086491438409</v>
       </c>
       <c r="R15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1393,49 +1369,49 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
         <v>48</v>
       </c>
       <c r="F16">
-        <v>0.8301797149836366</v>
+        <v>0.9037037037037038</v>
       </c>
       <c r="G16">
-        <v>0.08951796778677211</v>
+        <v>0.04274105425762929</v>
       </c>
       <c r="H16">
-        <v>0.6238095238095238</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I16">
-        <v>0.07284313590846836</v>
+        <v>0.07737179432986628</v>
       </c>
       <c r="J16">
-        <v>0.576936026936027</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="K16">
-        <v>0.1258777057728109</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="L16">
-        <v>0.6792341446727412</v>
+        <v>0.6768138294454085</v>
       </c>
       <c r="M16">
-        <v>0.1343152617788068</v>
+        <v>0.1520601981174081</v>
       </c>
       <c r="N16">
-        <v>0.576936026936027</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="O16">
-        <v>0.1258777057728109</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="P16">
-        <v>0.600674381050321</v>
+        <v>0.6398366314142327</v>
       </c>
       <c r="Q16">
-        <v>0.1417256994633832</v>
+        <v>0.1857086491438409</v>
       </c>
       <c r="R16" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1443,49 +1419,49 @@
         <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="F17">
-        <v>0.8296044006828319</v>
+        <v>0.9037037037037038</v>
       </c>
       <c r="G17">
-        <v>0.08772264830250585</v>
+        <v>0.04274105425762929</v>
       </c>
       <c r="H17">
-        <v>0.6333333333333333</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I17">
-        <v>0.08984743935292001</v>
+        <v>0.07737179432986628</v>
       </c>
       <c r="J17">
-        <v>0.5852120646238294</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="K17">
-        <v>0.1381295204989379</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="L17">
-        <v>0.6799455077086656</v>
+        <v>0.6768138294454085</v>
       </c>
       <c r="M17">
-        <v>0.1567783581067692</v>
+        <v>0.1520601981174081</v>
       </c>
       <c r="N17">
-        <v>0.5852120646238294</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="O17">
-        <v>0.1381295204989379</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="P17">
-        <v>0.6113756171025446</v>
+        <v>0.6398366314142327</v>
       </c>
       <c r="Q17">
-        <v>0.1519566667545583</v>
+        <v>0.1857086491438409</v>
       </c>
       <c r="R17" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1493,49 +1469,49 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
       </c>
       <c r="F18">
-        <v>0.8283424817738544</v>
+        <v>0.9037037037037038</v>
       </c>
       <c r="G18">
-        <v>0.08510354925349066</v>
+        <v>0.04398291122641866</v>
       </c>
       <c r="H18">
-        <v>0.6285714285714286</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I18">
-        <v>0.09712418121129111</v>
+        <v>0.07737179432986628</v>
       </c>
       <c r="J18">
-        <v>0.5816526610644257</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="K18">
-        <v>0.14372645212414</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="L18">
-        <v>0.6751029741182542</v>
+        <v>0.6768138294454085</v>
       </c>
       <c r="M18">
-        <v>0.1660160543283787</v>
+        <v>0.1520601981174081</v>
       </c>
       <c r="N18">
-        <v>0.5816526610644257</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="O18">
-        <v>0.14372645212414</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="P18">
-        <v>0.6085132116749193</v>
+        <v>0.6398366314142327</v>
       </c>
       <c r="Q18">
-        <v>0.15760033651757</v>
+        <v>0.1857086491438409</v>
       </c>
       <c r="R18" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1543,49 +1519,49 @@
         <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="F19">
-        <v>0.8256460496656575</v>
+        <v>0.9033670033670035</v>
       </c>
       <c r="G19">
-        <v>0.08522431075472751</v>
+        <v>0.04429369393266589</v>
       </c>
       <c r="H19">
-        <v>0.6333333333333333</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I19">
-        <v>0.1005652956282994</v>
+        <v>0.07737179432986628</v>
       </c>
       <c r="J19">
-        <v>0.5853563647681295</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="K19">
-        <v>0.1464905252734084</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="L19">
-        <v>0.6784370669260312</v>
+        <v>0.6768138294454085</v>
       </c>
       <c r="M19">
-        <v>0.1682977342335244</v>
+        <v>0.1520601981174081</v>
       </c>
       <c r="N19">
-        <v>0.5853563647681295</v>
+        <v>0.6505050505050505</v>
       </c>
       <c r="O19">
-        <v>0.1464905252734084</v>
+        <v>0.1723090084824329</v>
       </c>
       <c r="P19">
-        <v>0.6120230337893926</v>
+        <v>0.6398366314142327</v>
       </c>
       <c r="Q19">
-        <v>0.1602494826529754</v>
+        <v>0.1857086491438409</v>
       </c>
       <c r="R19" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -1593,49 +1569,49 @@
         <v>19</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="F20">
-        <v>0.8254687396844259</v>
+        <v>0.9030303030303031</v>
       </c>
       <c r="G20">
-        <v>0.08510740979564221</v>
+        <v>0.04181866978683724</v>
       </c>
       <c r="H20">
-        <v>0.6333333333333333</v>
+        <v>0.6761904761904762</v>
       </c>
       <c r="I20">
-        <v>0.1005652956282994</v>
+        <v>0.06998542122237651</v>
       </c>
       <c r="J20">
-        <v>0.5853563647681295</v>
+        <v>0.6430976430976431</v>
       </c>
       <c r="K20">
-        <v>0.1464905252734084</v>
+        <v>0.1648525560114348</v>
       </c>
       <c r="L20">
-        <v>0.6784370669260312</v>
+        <v>0.6697431223747013</v>
       </c>
       <c r="M20">
-        <v>0.1682977342335244</v>
+        <v>0.1452889408032716</v>
       </c>
       <c r="N20">
-        <v>0.5853563647681295</v>
+        <v>0.6430976430976431</v>
       </c>
       <c r="O20">
-        <v>0.1464905252734084</v>
+        <v>0.1648525560114348</v>
       </c>
       <c r="P20">
-        <v>0.6120230337893926</v>
+        <v>0.632849466532331</v>
       </c>
       <c r="Q20">
-        <v>0.1602494826529754</v>
+        <v>0.1788430450669794</v>
       </c>
       <c r="R20" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1649,43 +1625,43 @@
         <v>48</v>
       </c>
       <c r="F21">
-        <v>0.8254687396844259</v>
+        <v>0.8983164983164984</v>
       </c>
       <c r="G21">
-        <v>0.08510740979564221</v>
+        <v>0.04046852317964052</v>
       </c>
       <c r="H21">
-        <v>0.6333333333333333</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I21">
-        <v>0.1005652956282994</v>
+        <v>0.06023386019368343</v>
       </c>
       <c r="J21">
-        <v>0.5853563647681295</v>
+        <v>0.6356902356902356</v>
       </c>
       <c r="K21">
-        <v>0.1464905252734084</v>
+        <v>0.1581617352904425</v>
       </c>
       <c r="L21">
-        <v>0.6784370669260312</v>
+        <v>0.6595477621793411</v>
       </c>
       <c r="M21">
-        <v>0.1682977342335244</v>
+        <v>0.1342993313268816</v>
       </c>
       <c r="N21">
-        <v>0.5853563647681295</v>
+        <v>0.6356902356902356</v>
       </c>
       <c r="O21">
-        <v>0.1464905252734084</v>
+        <v>0.1581617352904425</v>
       </c>
       <c r="P21">
-        <v>0.6120230337893926</v>
+        <v>0.6241194295900179</v>
       </c>
       <c r="Q21">
-        <v>0.1602494826529754</v>
+        <v>0.171754278995742</v>
       </c>
       <c r="R21" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1693,93 +1669,99 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="F22">
-        <v>0.821489403842345</v>
+        <v>0.8794612794612794</v>
       </c>
       <c r="G22">
-        <v>0.07747365984503692</v>
+        <v>0.03272408569647896</v>
       </c>
       <c r="H22">
-        <v>0.5571428571428572</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="I22">
-        <v>0.07766431633476234</v>
+        <v>0.06023386019368339</v>
       </c>
       <c r="J22">
-        <v>0.5015986192456781</v>
+        <v>0.5461279461279462</v>
       </c>
       <c r="K22">
-        <v>0.1654177675424359</v>
+        <v>0.1414205546084675</v>
       </c>
       <c r="L22">
-        <v>0.5607088690176926</v>
+        <v>0.5581265031265031</v>
       </c>
       <c r="M22">
-        <v>0.1962793170890713</v>
+        <v>0.1399499612069821</v>
       </c>
       <c r="N22">
-        <v>0.5015986192456781</v>
+        <v>0.5461279461279462</v>
       </c>
       <c r="O22">
-        <v>0.1654177675424359</v>
+        <v>0.1414205546084675</v>
       </c>
       <c r="P22">
-        <v>0.5036161885598662</v>
+        <v>0.5359382542834347</v>
       </c>
       <c r="Q22">
-        <v>0.179332402952555</v>
+        <v>0.1492203602906791</v>
       </c>
       <c r="R22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
       </c>
       <c r="F23">
-        <v>0.8095901828744967</v>
+        <v>0.8781144781144782</v>
       </c>
       <c r="G23">
-        <v>0.08071268848785697</v>
+        <v>0.03735098042260847</v>
       </c>
       <c r="H23">
-        <v>0.5285714285714287</v>
+        <v>0.619047619047619</v>
       </c>
       <c r="I23">
-        <v>0.05302632726504783</v>
+        <v>0.1043281061914602</v>
       </c>
       <c r="J23">
-        <v>0.4046515575927341</v>
+        <v>0.608080808080808</v>
       </c>
       <c r="K23">
-        <v>0.07971159014257319</v>
+        <v>0.1853699720844202</v>
       </c>
       <c r="L23">
-        <v>0.4171102971102971</v>
+        <v>0.6062746512746513</v>
       </c>
       <c r="M23">
-        <v>0.1237392577675699</v>
+        <v>0.2005163725340008</v>
       </c>
       <c r="N23">
-        <v>0.4046515575927341</v>
+        <v>0.608080808080808</v>
       </c>
       <c r="O23">
-        <v>0.07971159014257319</v>
+        <v>0.1853699720844202</v>
       </c>
       <c r="P23">
-        <v>0.3940717753011606</v>
+        <v>0.6028079860842009</v>
       </c>
       <c r="Q23">
-        <v>0.09990871333358566</v>
+        <v>0.1915028932152099</v>
       </c>
       <c r="R23" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -1787,49 +1769,49 @@
         <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="F24">
-        <v>0.8071138556432675</v>
+        <v>0.8760942760942761</v>
       </c>
       <c r="G24">
-        <v>0.07870027691024861</v>
+        <v>0.03409828660248394</v>
       </c>
       <c r="H24">
-        <v>0.5619047619047619</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="I24">
-        <v>0.07315376902732007</v>
+        <v>0.06998542122237651</v>
       </c>
       <c r="J24">
-        <v>0.4602354072942308</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="K24">
-        <v>0.1335192114195158</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="L24">
-        <v>0.5079082491582492</v>
+        <v>0.5657882857882858</v>
       </c>
       <c r="M24">
-        <v>0.2133071939135543</v>
+        <v>0.1515711603684023</v>
       </c>
       <c r="N24">
-        <v>0.4602354072942308</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="O24">
-        <v>0.1335192114195158</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="P24">
-        <v>0.4618416307990675</v>
+        <v>0.5420124230813886</v>
       </c>
       <c r="Q24">
-        <v>0.1628441422377386</v>
+        <v>0.158593877095747</v>
       </c>
       <c r="R24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1837,49 +1819,49 @@
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="F25">
-        <v>0.8060789972554678</v>
+        <v>0.8757575757575757</v>
       </c>
       <c r="G25">
-        <v>0.08612957408232831</v>
+        <v>0.03450808882240797</v>
       </c>
       <c r="H25">
-        <v>0.5666666666666667</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="I25">
-        <v>0.0816496580927726</v>
+        <v>0.06023386019368339</v>
       </c>
       <c r="J25">
-        <v>0.4641569759216818</v>
+        <v>0.5461279461279462</v>
       </c>
       <c r="K25">
-        <v>0.1384993910970991</v>
+        <v>0.1414205546084675</v>
       </c>
       <c r="L25">
-        <v>0.508688479155665</v>
+        <v>0.5581265031265031</v>
       </c>
       <c r="M25">
-        <v>0.2186103724681224</v>
+        <v>0.1399499612069821</v>
       </c>
       <c r="N25">
-        <v>0.4641569759216818</v>
+        <v>0.5461279461279462</v>
       </c>
       <c r="O25">
-        <v>0.1384993910970991</v>
+        <v>0.1414205546084675</v>
       </c>
       <c r="P25">
-        <v>0.4660962176093331</v>
+        <v>0.5359382542834347</v>
       </c>
       <c r="Q25">
-        <v>0.1685524666513119</v>
+        <v>0.1492203602906791</v>
       </c>
       <c r="R25" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -1887,49 +1869,49 @@
         <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="F26">
-        <v>0.8036216506804742</v>
+        <v>0.874074074074074</v>
       </c>
       <c r="G26">
-        <v>0.08574452109265841</v>
+        <v>0.03922811800926655</v>
       </c>
       <c r="H26">
-        <v>0.5809523809523809</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="I26">
-        <v>0.08329931278350429</v>
+        <v>0.06998542122237651</v>
       </c>
       <c r="J26">
-        <v>0.4744277508983391</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="K26">
-        <v>0.1426381581570114</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="L26">
-        <v>0.5203069487983282</v>
+        <v>0.5657882857882858</v>
       </c>
       <c r="M26">
-        <v>0.2201655345697633</v>
+        <v>0.1515711603684023</v>
       </c>
       <c r="N26">
-        <v>0.4744277508983391</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="O26">
-        <v>0.1426381581570114</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="P26">
-        <v>0.4798035451138898</v>
+        <v>0.5420124230813886</v>
       </c>
       <c r="Q26">
-        <v>0.1709746693466372</v>
+        <v>0.158593877095747</v>
       </c>
       <c r="R26" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1937,49 +1919,49 @@
         <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="F27">
-        <v>0.8034007205575833</v>
+        <v>0.8737373737373737</v>
       </c>
       <c r="G27">
-        <v>0.08891019349313521</v>
+        <v>0.03700641525665753</v>
       </c>
       <c r="H27">
-        <v>0.5571428571428572</v>
+        <v>0.619047619047619</v>
       </c>
       <c r="I27">
-        <v>0.0649437223665993</v>
+        <v>0.07968190728895956</v>
       </c>
       <c r="J27">
-        <v>0.4435687406275641</v>
+        <v>0.5461279461279462</v>
       </c>
       <c r="K27">
-        <v>0.1159415688782123</v>
+        <v>0.1576591911264809</v>
       </c>
       <c r="L27">
-        <v>0.5046565113500597</v>
+        <v>0.5588285788285788</v>
       </c>
       <c r="M27">
-        <v>0.2130757797845049</v>
+        <v>0.1604380696900342</v>
       </c>
       <c r="N27">
-        <v>0.4435687406275641</v>
+        <v>0.5461279461279462</v>
       </c>
       <c r="O27">
-        <v>0.1159415688782123</v>
+        <v>0.1576591911264809</v>
       </c>
       <c r="P27">
-        <v>0.443112052461646</v>
+        <v>0.5362738609898854</v>
       </c>
       <c r="Q27">
-        <v>0.1421006230315503</v>
+        <v>0.1647518707956543</v>
       </c>
       <c r="R27" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -1987,49 +1969,49 @@
         <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="F28">
-        <v>0.8020923520923521</v>
+        <v>0.8727272727272727</v>
       </c>
       <c r="G28">
-        <v>0.08397592009681053</v>
+        <v>0.02967168732238153</v>
       </c>
       <c r="H28">
-        <v>0.5761904761904761</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="I28">
-        <v>0.08024904545882246</v>
+        <v>0.06998542122237651</v>
       </c>
       <c r="J28">
-        <v>0.4712531477237359</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="K28">
-        <v>0.1387421213982867</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="L28">
-        <v>0.5172869792821949</v>
+        <v>0.5657882857882858</v>
       </c>
       <c r="M28">
-        <v>0.2170409156800077</v>
+        <v>0.1515711603684023</v>
       </c>
       <c r="N28">
-        <v>0.4712531477237359</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="O28">
-        <v>0.1387421213982867</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="P28">
-        <v>0.4763174847472134</v>
+        <v>0.5420124230813886</v>
       </c>
       <c r="Q28">
-        <v>0.1668117480998068</v>
+        <v>0.158593877095747</v>
       </c>
       <c r="R28" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2037,49 +2019,49 @@
         <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D29" t="s">
         <v>48</v>
       </c>
       <c r="F29">
-        <v>0.8019070254364372</v>
+        <v>0.869023569023569</v>
       </c>
       <c r="G29">
-        <v>0.08307660192329828</v>
+        <v>0.03031051160923067</v>
       </c>
       <c r="H29">
-        <v>0.5714285714285714</v>
+        <v>0.638095238095238</v>
       </c>
       <c r="I29">
-        <v>0.07221786137191952</v>
+        <v>0.0645936188869073</v>
       </c>
       <c r="J29">
-        <v>0.4668024785671845</v>
+        <v>0.6188552188552189</v>
       </c>
       <c r="K29">
-        <v>0.1333090708950869</v>
+        <v>0.1377659944077618</v>
       </c>
       <c r="L29">
-        <v>0.5140010063036379</v>
+        <v>0.6353853553853555</v>
       </c>
       <c r="M29">
-        <v>0.2126554589744239</v>
+        <v>0.1289214891925226</v>
       </c>
       <c r="N29">
-        <v>0.4668024785671845</v>
+        <v>0.6188552188552189</v>
       </c>
       <c r="O29">
-        <v>0.1333090708950869</v>
+        <v>0.1377659944077618</v>
       </c>
       <c r="P29">
-        <v>0.4721257777106323</v>
+        <v>0.6104568675258332</v>
       </c>
       <c r="Q29">
-        <v>0.1615774494007572</v>
+        <v>0.1473529272586317</v>
       </c>
       <c r="R29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -2087,49 +2069,49 @@
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
         <v>48</v>
       </c>
       <c r="F30">
-        <v>0.8018994803308528</v>
+        <v>0.869023569023569</v>
       </c>
       <c r="G30">
-        <v>0.08387619634086084</v>
+        <v>0.03106779090753474</v>
       </c>
       <c r="H30">
-        <v>0.5761904761904763</v>
+        <v>0.638095238095238</v>
       </c>
       <c r="I30">
-        <v>0.07589227357385346</v>
+        <v>0.0645936188869073</v>
       </c>
       <c r="J30">
-        <v>0.4714710126474833</v>
+        <v>0.6188552188552189</v>
       </c>
       <c r="K30">
-        <v>0.1314946646751267</v>
+        <v>0.1377659944077618</v>
       </c>
       <c r="L30">
-        <v>0.5173630982682706</v>
+        <v>0.6353853553853555</v>
       </c>
       <c r="M30">
-        <v>0.2104807474431211</v>
+        <v>0.1289214891925226</v>
       </c>
       <c r="N30">
-        <v>0.4714710126474833</v>
+        <v>0.6188552188552189</v>
       </c>
       <c r="O30">
-        <v>0.1314946646751267</v>
+        <v>0.1377659944077618</v>
       </c>
       <c r="P30">
-        <v>0.4773807369101486</v>
+        <v>0.6104568675258332</v>
       </c>
       <c r="Q30">
-        <v>0.159832234165356</v>
+        <v>0.1473529272586317</v>
       </c>
       <c r="R30" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2137,99 +2119,93 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
       </c>
       <c r="F31">
-        <v>0.8012597968480322</v>
+        <v>0.8686868686868687</v>
       </c>
       <c r="G31">
-        <v>0.08026867749176134</v>
+        <v>0.02990763365818513</v>
       </c>
       <c r="H31">
-        <v>0.5714285714285714</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="I31">
-        <v>0.07221786137191952</v>
+        <v>0.06998542122237651</v>
       </c>
       <c r="J31">
-        <v>0.4668024785671845</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="K31">
-        <v>0.1333090708950869</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="L31">
-        <v>0.5140010063036379</v>
+        <v>0.5657882857882858</v>
       </c>
       <c r="M31">
-        <v>0.2126554589744239</v>
+        <v>0.1515711603684023</v>
       </c>
       <c r="N31">
-        <v>0.4668024785671845</v>
+        <v>0.5521885521885522</v>
       </c>
       <c r="O31">
-        <v>0.1333090708950869</v>
+        <v>0.1508327318131022</v>
       </c>
       <c r="P31">
-        <v>0.4721257777106323</v>
+        <v>0.5420124230813886</v>
       </c>
       <c r="Q31">
-        <v>0.1615774494007572</v>
+        <v>0.158593877095747</v>
       </c>
       <c r="R31" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="F32">
-        <v>0.8003958822586273</v>
+        <v>0.8621212121212121</v>
       </c>
       <c r="G32">
-        <v>0.07916816907416739</v>
+        <v>0.06263078800492046</v>
       </c>
       <c r="H32">
-        <v>0.5714285714285714</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="I32">
-        <v>0.07221786137191952</v>
+        <v>0.07377111135633174</v>
       </c>
       <c r="J32">
-        <v>0.4668024785671845</v>
+        <v>0.4774410774410774</v>
       </c>
       <c r="K32">
-        <v>0.1333090708950869</v>
+        <v>0.1335032757068958</v>
       </c>
       <c r="L32">
-        <v>0.5140010063036379</v>
+        <v>0.4889248006895065</v>
       </c>
       <c r="M32">
-        <v>0.2126554589744239</v>
+        <v>0.1372782687021845</v>
       </c>
       <c r="N32">
-        <v>0.4668024785671845</v>
+        <v>0.4774410774410774</v>
       </c>
       <c r="O32">
-        <v>0.1333090708950869</v>
+        <v>0.1335032757068958</v>
       </c>
       <c r="P32">
-        <v>0.4721257777106323</v>
+        <v>0.4611043277709945</v>
       </c>
       <c r="Q32">
-        <v>0.1615774494007572</v>
+        <v>0.1412098038020484</v>
       </c>
       <c r="R32" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2237,43 +2213,43 @@
         <v>22</v>
       </c>
       <c r="F33">
-        <v>0.7963486404662875</v>
+        <v>0.8348484848484847</v>
       </c>
       <c r="G33">
-        <v>0.07185677370213728</v>
+        <v>0.04051751741440727</v>
       </c>
       <c r="H33">
-        <v>0.5666666666666667</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="I33">
-        <v>0.06801360408136047</v>
+        <v>0.07126966450997983</v>
       </c>
       <c r="J33">
-        <v>0.5078686019862491</v>
+        <v>0.7797979797979797</v>
       </c>
       <c r="K33">
-        <v>0.07053844269534618</v>
+        <v>0.05402335655254298</v>
       </c>
       <c r="L33">
-        <v>0.5685573685573686</v>
+        <v>0.7850297850297852</v>
       </c>
       <c r="M33">
-        <v>0.1383853538912211</v>
+        <v>0.05352408522574237</v>
       </c>
       <c r="N33">
-        <v>0.5078686019862491</v>
+        <v>0.7797979797979797</v>
       </c>
       <c r="O33">
-        <v>0.07053844269534618</v>
+        <v>0.05402335655254298</v>
       </c>
       <c r="P33">
-        <v>0.525006207608065</v>
+        <v>0.7747651958178274</v>
       </c>
       <c r="Q33">
-        <v>0.09553608206736325</v>
+        <v>0.0535462308563333</v>
       </c>
       <c r="R33" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -2281,43 +2257,43 @@
         <v>23</v>
       </c>
       <c r="F34">
-        <v>0.7387337426553112</v>
+        <v>0.8301346801346801</v>
       </c>
       <c r="G34">
-        <v>0.07406902674079696</v>
+        <v>0.04184915653710424</v>
       </c>
       <c r="H34">
-        <v>0.5523809523809524</v>
+        <v>0.638095238095238</v>
       </c>
       <c r="I34">
-        <v>0.06966066113489429</v>
+        <v>0.09805362039035238</v>
       </c>
       <c r="J34">
-        <v>0.4079761197408256</v>
+        <v>0.6835016835016836</v>
       </c>
       <c r="K34">
-        <v>0.08197305398097594</v>
+        <v>0.1539865777790667</v>
       </c>
       <c r="L34">
-        <v>0.4385350884862932</v>
+        <v>0.6582659932659933</v>
       </c>
       <c r="M34">
-        <v>0.1649244772618563</v>
+        <v>0.1810139370735496</v>
       </c>
       <c r="N34">
-        <v>0.4079761197408256</v>
+        <v>0.6835016835016836</v>
       </c>
       <c r="O34">
-        <v>0.08197305398097594</v>
+        <v>0.1539865777790667</v>
       </c>
       <c r="P34">
-        <v>0.4010022586109543</v>
+        <v>0.6568251211388466</v>
       </c>
       <c r="Q34">
-        <v>0.1057469074239933</v>
+        <v>0.1645823064520534</v>
       </c>
       <c r="R34" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2325,43 +2301,43 @@
         <v>24</v>
       </c>
       <c r="F35">
-        <v>0.7367540955776251</v>
+        <v>0.8218855218855218</v>
       </c>
       <c r="G35">
-        <v>0.07279116258620412</v>
+        <v>0.03266860935110348</v>
       </c>
       <c r="H35">
-        <v>0.5238095238095238</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="I35">
-        <v>0.05429406786186371</v>
+        <v>0.03563483225498991</v>
       </c>
       <c r="J35">
-        <v>0.4066915655150948</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="K35">
-        <v>0.08261391072397035</v>
+        <v>0.1034804540879004</v>
       </c>
       <c r="L35">
-        <v>0.4192245105517417</v>
+        <v>0.4871428571428572</v>
       </c>
       <c r="M35">
-        <v>0.1482859267678411</v>
+        <v>0.1043406634485272</v>
       </c>
       <c r="N35">
-        <v>0.4066915655150948</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="O35">
-        <v>0.08261391072397035</v>
+        <v>0.1034804540879004</v>
       </c>
       <c r="P35">
-        <v>0.4012351721577078</v>
+        <v>0.478542002754279</v>
       </c>
       <c r="Q35">
-        <v>0.1060114589868047</v>
+        <v>0.1083616778753374</v>
       </c>
       <c r="R35" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2369,43 +2345,43 @@
         <v>25</v>
       </c>
       <c r="F36">
-        <v>0.7096558488715351</v>
+        <v>0.77003367003367</v>
       </c>
       <c r="G36">
-        <v>0.1002224799749673</v>
+        <v>0.1258854073345903</v>
       </c>
       <c r="H36">
-        <v>0.5571428571428572</v>
+        <v>0.5619047619047619</v>
       </c>
       <c r="I36">
-        <v>0.08857654875113465</v>
+        <v>0.1016864595431553</v>
       </c>
       <c r="J36">
-        <v>0.5139320374614492</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="K36">
-        <v>0.1665723446258096</v>
+        <v>0.1243331815641529</v>
       </c>
       <c r="L36">
-        <v>0.5693542045715959</v>
+        <v>0.5091092241092241</v>
       </c>
       <c r="M36">
-        <v>0.1931297332756028</v>
+        <v>0.1307205256130821</v>
       </c>
       <c r="N36">
-        <v>0.5139320374614492</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="O36">
-        <v>0.1665723446258096</v>
+        <v>0.1243331815641529</v>
       </c>
       <c r="P36">
-        <v>0.5221797429692167</v>
+        <v>0.502593247825446</v>
       </c>
       <c r="Q36">
-        <v>0.1760475057505096</v>
+        <v>0.1299304064411619</v>
       </c>
       <c r="R36" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2413,43 +2389,43 @@
         <v>26</v>
       </c>
       <c r="F37">
-        <v>0.7016028633675693</v>
+        <v>0.7626262626262627</v>
       </c>
       <c r="G37">
-        <v>0.07669503898490206</v>
+        <v>0.07814059704980317</v>
       </c>
       <c r="H37">
-        <v>0.5190476190476191</v>
+        <v>0.6285714285714287</v>
       </c>
       <c r="I37">
-        <v>0.04096345365258394</v>
+        <v>0.0761904761904762</v>
       </c>
       <c r="J37">
-        <v>0.3689245395127748</v>
+        <v>0.4457912457912457</v>
       </c>
       <c r="K37">
-        <v>0.07525725764311546</v>
+        <v>0.05728261365154675</v>
       </c>
       <c r="L37">
-        <v>0.306981826547044</v>
+        <v>0.4307511007511007</v>
       </c>
       <c r="M37">
-        <v>0.2138501345861229</v>
+        <v>0.05782042512673727</v>
       </c>
       <c r="N37">
-        <v>0.3689245395127748</v>
+        <v>0.4457912457912457</v>
       </c>
       <c r="O37">
-        <v>0.07525725764311546</v>
+        <v>0.05728261365154675</v>
       </c>
       <c r="P37">
-        <v>0.3090823193409401</v>
+        <v>0.427738560278606</v>
       </c>
       <c r="Q37">
-        <v>0.1317141542120268</v>
+        <v>0.0515182537095065</v>
       </c>
       <c r="R37" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2457,43 +2433,43 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>0.6986234897999604</v>
+        <v>0.7555555555555556</v>
       </c>
       <c r="G38">
-        <v>0.08809607672407975</v>
+        <v>0.08256987969758248</v>
       </c>
       <c r="H38">
-        <v>0.5380952380952381</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="I38">
-        <v>0.06317380553057905</v>
+        <v>0.06998542122237654</v>
       </c>
       <c r="J38">
-        <v>0.5044039838157485</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="K38">
-        <v>0.1118224202499437</v>
+        <v>0.1132635110246589</v>
       </c>
       <c r="L38">
-        <v>0.5185580350162393</v>
+        <v>0.4927091427091426</v>
       </c>
       <c r="M38">
-        <v>0.1381123244686045</v>
+        <v>0.1202735814850901</v>
       </c>
       <c r="N38">
-        <v>0.5044039838157485</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="O38">
-        <v>0.1118224202499437</v>
+        <v>0.1132635110246589</v>
       </c>
       <c r="P38">
-        <v>0.5049069096884763</v>
+        <v>0.489204345954918</v>
       </c>
       <c r="Q38">
-        <v>0.121824934124675</v>
+        <v>0.1137665152636037</v>
       </c>
       <c r="R38" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2501,43 +2477,43 @@
         <v>28</v>
       </c>
       <c r="F39">
-        <v>0.6986234897999604</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="G39">
-        <v>0.08809607672407975</v>
+        <v>0.15489459765566</v>
       </c>
       <c r="H39">
-        <v>0.5285714285714286</v>
+        <v>0.5619047619047619</v>
       </c>
       <c r="I39">
-        <v>0.0590936840285279</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="J39">
-        <v>0.4106131341425459</v>
+        <v>0.5717171717171718</v>
       </c>
       <c r="K39">
-        <v>0.08326675628202511</v>
+        <v>0.1867445822006173</v>
       </c>
       <c r="L39">
-        <v>0.4241837329897634</v>
+        <v>0.5629292929292929</v>
       </c>
       <c r="M39">
-        <v>0.1468719028457077</v>
+        <v>0.196820372572737</v>
       </c>
       <c r="N39">
-        <v>0.4106131341425459</v>
+        <v>0.5717171717171718</v>
       </c>
       <c r="O39">
-        <v>0.08326675628202511</v>
+        <v>0.1867445822006173</v>
       </c>
       <c r="P39">
-        <v>0.4045612488136349</v>
+        <v>0.5613519813519814</v>
       </c>
       <c r="Q39">
-        <v>0.1060489907948798</v>
+        <v>0.1940420678348387</v>
       </c>
       <c r="R39" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2545,43 +2521,43 @@
         <v>29</v>
       </c>
       <c r="F40">
-        <v>0.6868273066802479</v>
+        <v>0.7478114478114478</v>
       </c>
       <c r="G40">
-        <v>0.04967504977389266</v>
+        <v>0.0691560689318295</v>
       </c>
       <c r="H40">
-        <v>0.5523809523809524</v>
+        <v>0.6095238095238095</v>
       </c>
       <c r="I40">
-        <v>0.05302632726504784</v>
+        <v>0.03563483225498992</v>
       </c>
       <c r="J40">
-        <v>0.5824364089069971</v>
+        <v>0.5468013468013468</v>
       </c>
       <c r="K40">
-        <v>0.06623339969852346</v>
+        <v>0.1366289973245327</v>
       </c>
       <c r="L40">
-        <v>0.6500685257054439</v>
+        <v>0.5351348651348651</v>
       </c>
       <c r="M40">
-        <v>0.04704499430786618</v>
+        <v>0.1478435248983235</v>
       </c>
       <c r="N40">
-        <v>0.5824364089069971</v>
+        <v>0.5468013468013468</v>
       </c>
       <c r="O40">
-        <v>0.06623339969852346</v>
+        <v>0.1366289973245327</v>
       </c>
       <c r="P40">
-        <v>0.5975219686896155</v>
+        <v>0.5365772720571482</v>
       </c>
       <c r="Q40">
-        <v>0.04556873395632757</v>
+        <v>0.1440041206503067</v>
       </c>
       <c r="R40" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2589,43 +2565,43 @@
         <v>30</v>
       </c>
       <c r="F41">
-        <v>0.6858123720868818</v>
+        <v>0.7478114478114478</v>
       </c>
       <c r="G41">
-        <v>0.05737155270771935</v>
+        <v>0.0691560689318295</v>
       </c>
       <c r="H41">
-        <v>0.5095238095238095</v>
+        <v>0.5809523809523809</v>
       </c>
       <c r="I41">
-        <v>0.05128728387747148</v>
+        <v>0.05553287518900284</v>
       </c>
       <c r="J41">
-        <v>0.3940723764253176</v>
+        <v>0.4087542087542088</v>
       </c>
       <c r="K41">
-        <v>0.04498601180554068</v>
+        <v>0.03728718707045692</v>
       </c>
       <c r="L41">
-        <v>0.3810752371123888</v>
+        <v>0.3933993783993784</v>
       </c>
       <c r="M41">
-        <v>0.06340234118176359</v>
+        <v>0.0326314249522393</v>
       </c>
       <c r="N41">
-        <v>0.3940723764253176</v>
+        <v>0.4087542087542088</v>
       </c>
       <c r="O41">
-        <v>0.04498601180554068</v>
+        <v>0.03728718707045692</v>
       </c>
       <c r="P41">
-        <v>0.3769799377646674</v>
+        <v>0.3939732128896215</v>
       </c>
       <c r="Q41">
-        <v>0.05005395096188176</v>
+        <v>0.03899283448686797</v>
       </c>
       <c r="R41" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -2633,43 +2609,43 @@
         <v>31</v>
       </c>
       <c r="F42">
-        <v>0.6706047402125833</v>
+        <v>0.7456228956228956</v>
       </c>
       <c r="G42">
-        <v>0.09287489121394329</v>
+        <v>0.06200316359324534</v>
       </c>
       <c r="H42">
-        <v>0.5142857142857142</v>
+        <v>0.5619047619047619</v>
       </c>
       <c r="I42">
-        <v>0.0534522483824849</v>
+        <v>0.1016864595431553</v>
       </c>
       <c r="J42">
-        <v>0.4102099425628838</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="K42">
-        <v>0.05494541900364228</v>
+        <v>0.1243331815641529</v>
       </c>
       <c r="L42">
-        <v>0.4480007029508982</v>
+        <v>0.5091092241092241</v>
       </c>
       <c r="M42">
-        <v>0.1372625873247162</v>
+        <v>0.1307205256130821</v>
       </c>
       <c r="N42">
-        <v>0.4102099425628838</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="O42">
-        <v>0.05494541900364228</v>
+        <v>0.1243331815641529</v>
       </c>
       <c r="P42">
-        <v>0.4051513263708386</v>
+        <v>0.502593247825446</v>
       </c>
       <c r="Q42">
-        <v>0.07036776941964075</v>
+        <v>0.1299304064411619</v>
       </c>
       <c r="R42" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2677,43 +2653,43 @@
         <v>32</v>
       </c>
       <c r="F43">
-        <v>0.6706047402125833</v>
+        <v>0.7456228956228956</v>
       </c>
       <c r="G43">
-        <v>0.09287489121394329</v>
+        <v>0.06200316359324534</v>
       </c>
       <c r="H43">
-        <v>0.5047619047619047</v>
+        <v>0.5523809523809524</v>
       </c>
       <c r="I43">
-        <v>0.05512303287042965</v>
+        <v>0.1069044967649698</v>
       </c>
       <c r="J43">
-        <v>0.3718501542030954</v>
+        <v>0.5077441077441077</v>
       </c>
       <c r="K43">
-        <v>0.04002304466485461</v>
+        <v>0.134062557108838</v>
       </c>
       <c r="L43">
-        <v>0.3455196815568332</v>
+        <v>0.5043473193473194</v>
       </c>
       <c r="M43">
-        <v>0.0353818276613035</v>
+        <v>0.1368594707900541</v>
       </c>
       <c r="N43">
-        <v>0.3718501542030954</v>
+        <v>0.5077441077441077</v>
       </c>
       <c r="O43">
-        <v>0.04002304466485461</v>
+        <v>0.134062557108838</v>
       </c>
       <c r="P43">
-        <v>0.3495546177077684</v>
+        <v>0.4962206988058382</v>
       </c>
       <c r="Q43">
-        <v>0.03734526040279561</v>
+        <v>0.1377407117985731</v>
       </c>
       <c r="R43" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -2721,43 +2697,43 @@
         <v>33</v>
       </c>
       <c r="F44">
-        <v>0.6666834073696819</v>
+        <v>0.7370370370370369</v>
       </c>
       <c r="G44">
-        <v>0.07487229830196605</v>
+        <v>0.106779138404547</v>
       </c>
       <c r="H44">
-        <v>0.5095238095238095</v>
+        <v>0.5047619047619046</v>
       </c>
       <c r="I44">
-        <v>0.04416008807378907</v>
+        <v>0.08832017614757814</v>
       </c>
       <c r="J44">
-        <v>0.3773392185156891</v>
+        <v>0.4127946127946128</v>
       </c>
       <c r="K44">
-        <v>0.03444373954258947</v>
+        <v>0.1640197252450864</v>
       </c>
       <c r="L44">
-        <v>0.3498944437130599</v>
+        <v>0.328042328042328</v>
       </c>
       <c r="M44">
-        <v>0.02851134751405206</v>
+        <v>0.2780623384983138</v>
       </c>
       <c r="N44">
-        <v>0.3773392185156891</v>
+        <v>0.4127946127946128</v>
       </c>
       <c r="O44">
-        <v>0.03444373954258947</v>
+        <v>0.1640197252450864</v>
       </c>
       <c r="P44">
-        <v>0.3512255009038497</v>
+        <v>0.3296504702194357</v>
       </c>
       <c r="Q44">
-        <v>0.03092971388061817</v>
+        <v>0.1932604337864895</v>
       </c>
       <c r="R44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -2765,43 +2741,43 @@
         <v>34</v>
       </c>
       <c r="F45">
-        <v>0.6622079808354318</v>
+        <v>0.7336700336700337</v>
       </c>
       <c r="G45">
-        <v>0.07044289809944522</v>
+        <v>0.1008888160742123</v>
       </c>
       <c r="H45">
-        <v>0.5095238095238095</v>
+        <v>0.5904761904761904</v>
       </c>
       <c r="I45">
-        <v>0.04416008807378907</v>
+        <v>0.04856209060564556</v>
       </c>
       <c r="J45">
-        <v>0.3960020371785078</v>
+        <v>0.4134680134680134</v>
       </c>
       <c r="K45">
-        <v>0.04148002121784966</v>
+        <v>0.03533910239300183</v>
       </c>
       <c r="L45">
-        <v>0.3817357135543297</v>
+        <v>0.3973976023976025</v>
       </c>
       <c r="M45">
-        <v>0.06062981225852353</v>
+        <v>0.03280991277176423</v>
       </c>
       <c r="N45">
-        <v>0.3960020371785078</v>
+        <v>0.4134680134680134</v>
       </c>
       <c r="O45">
-        <v>0.04148002121784966</v>
+        <v>0.03533910239300183</v>
       </c>
       <c r="P45">
-        <v>0.3765826654276366</v>
+        <v>0.3996335539046536</v>
       </c>
       <c r="Q45">
-        <v>0.04725549138407344</v>
+        <v>0.0341667466906558</v>
       </c>
       <c r="R45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -2809,43 +2785,43 @@
         <v>35</v>
       </c>
       <c r="F46">
-        <v>0.6576644125663733</v>
+        <v>0.7323232323232324</v>
       </c>
       <c r="G46">
-        <v>0.0509523819737417</v>
+        <v>0.1102969867980917</v>
       </c>
       <c r="H46">
-        <v>0.5047619047619047</v>
+        <v>0.619047619047619</v>
       </c>
       <c r="I46">
-        <v>0.04616837959444124</v>
+        <v>0.07968190728895957</v>
       </c>
       <c r="J46">
-        <v>0.3736355148119854</v>
+        <v>0.4383838383838384</v>
       </c>
       <c r="K46">
-        <v>0.03622786622811783</v>
+        <v>0.06058360975861268</v>
       </c>
       <c r="L46">
-        <v>0.344949388768005</v>
+        <v>0.4234783734783735</v>
       </c>
       <c r="M46">
-        <v>0.03093158594074248</v>
+        <v>0.06149532399326973</v>
       </c>
       <c r="N46">
-        <v>0.3736355148119854</v>
+        <v>0.4383838383838384</v>
       </c>
       <c r="O46">
-        <v>0.03622786622811783</v>
+        <v>0.06058360975861268</v>
       </c>
       <c r="P46">
-        <v>0.3482606161998346</v>
+        <v>0.4208060775566496</v>
       </c>
       <c r="Q46">
-        <v>0.03246088037632762</v>
+        <v>0.05406340322775361</v>
       </c>
       <c r="R46" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -2853,43 +2829,43 @@
         <v>36</v>
       </c>
       <c r="F47">
-        <v>0.6354490280960869</v>
+        <v>0.6787878787878788</v>
       </c>
       <c r="G47">
-        <v>0.1249292584693572</v>
+        <v>0.1400584366504629</v>
       </c>
       <c r="H47">
-        <v>0.5571428571428572</v>
+        <v>0.5619047619047619</v>
       </c>
       <c r="I47">
-        <v>0.08857654875113465</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="J47">
-        <v>0.5139320374614492</v>
+        <v>0.5717171717171718</v>
       </c>
       <c r="K47">
-        <v>0.1665723446258096</v>
+        <v>0.1867445822006173</v>
       </c>
       <c r="L47">
-        <v>0.5693542045715959</v>
+        <v>0.5629292929292929</v>
       </c>
       <c r="M47">
-        <v>0.1931297332756028</v>
+        <v>0.196820372572737</v>
       </c>
       <c r="N47">
-        <v>0.5139320374614492</v>
+        <v>0.5717171717171718</v>
       </c>
       <c r="O47">
-        <v>0.1665723446258096</v>
+        <v>0.1867445822006173</v>
       </c>
       <c r="P47">
-        <v>0.5221797429692167</v>
+        <v>0.5613519813519814</v>
       </c>
       <c r="Q47">
-        <v>0.1760475057505096</v>
+        <v>0.1940420678348387</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -2897,43 +2873,43 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>0.6354490280960869</v>
+        <v>0.6787878787878788</v>
       </c>
       <c r="G48">
-        <v>0.1249292584693572</v>
+        <v>0.1400584366504629</v>
       </c>
       <c r="H48">
-        <v>0.5571428571428572</v>
+        <v>0.5619047619047619</v>
       </c>
       <c r="I48">
-        <v>0.08857654875113465</v>
+        <v>0.1142857142857143</v>
       </c>
       <c r="J48">
-        <v>0.5139320374614492</v>
+        <v>0.5717171717171718</v>
       </c>
       <c r="K48">
-        <v>0.1665723446258096</v>
+        <v>0.1867445822006173</v>
       </c>
       <c r="L48">
-        <v>0.5693542045715959</v>
+        <v>0.5629292929292929</v>
       </c>
       <c r="M48">
-        <v>0.1931297332756028</v>
+        <v>0.196820372572737</v>
       </c>
       <c r="N48">
-        <v>0.5139320374614492</v>
+        <v>0.5717171717171718</v>
       </c>
       <c r="O48">
-        <v>0.1665723446258096</v>
+        <v>0.1867445822006173</v>
       </c>
       <c r="P48">
-        <v>0.5221797429692167</v>
+        <v>0.5613519813519814</v>
       </c>
       <c r="Q48">
-        <v>0.1760475057505096</v>
+        <v>0.1940420678348387</v>
       </c>
       <c r="R48" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
